--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12397200</v>
+        <v>13361900</v>
       </c>
       <c r="E8" s="3">
-        <v>11565000</v>
+        <v>12432600</v>
       </c>
       <c r="F8" s="3">
-        <v>10535400</v>
+        <v>11598100</v>
       </c>
       <c r="G8" s="3">
-        <v>8916500</v>
+        <v>10565500</v>
       </c>
       <c r="H8" s="3">
-        <v>6955900</v>
+        <v>8942000</v>
       </c>
       <c r="I8" s="3">
-        <v>5690800</v>
+        <v>6975800</v>
       </c>
       <c r="J8" s="3">
+        <v>5707100</v>
+      </c>
+      <c r="K8" s="3">
         <v>4801100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4626900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4467000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4179100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4479600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3846000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4143300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4898200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5964000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6438300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7751700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8073600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7778900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7110400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6720900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7042600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -951,8 +957,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1052,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1277,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,8 +1372,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,8 +1467,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9034800</v>
+        <v>10384800</v>
       </c>
       <c r="E17" s="3">
-        <v>8082200</v>
+        <v>9060600</v>
       </c>
       <c r="F17" s="3">
-        <v>7223900</v>
+        <v>8105300</v>
       </c>
       <c r="G17" s="3">
-        <v>5242700</v>
+        <v>7244600</v>
       </c>
       <c r="H17" s="3">
-        <v>3360200</v>
+        <v>5257700</v>
       </c>
       <c r="I17" s="3">
-        <v>2286100</v>
+        <v>3369800</v>
       </c>
       <c r="J17" s="3">
+        <v>2292600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1996400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1733500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1605700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1446300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1589100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1539000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1706300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2354200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2969500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2912700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3733800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3942100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3931900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3275500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3102400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3343400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3362400</v>
+        <v>2977000</v>
       </c>
       <c r="E18" s="3">
-        <v>3482900</v>
+        <v>3372000</v>
       </c>
       <c r="F18" s="3">
-        <v>3311400</v>
+        <v>3492800</v>
       </c>
       <c r="G18" s="3">
-        <v>3673800</v>
+        <v>3320900</v>
       </c>
       <c r="H18" s="3">
-        <v>3595700</v>
+        <v>3684300</v>
       </c>
       <c r="I18" s="3">
-        <v>3404700</v>
+        <v>3606000</v>
       </c>
       <c r="J18" s="3">
+        <v>3414500</v>
+      </c>
+      <c r="K18" s="3">
         <v>2804700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2893500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2861300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2732800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2890500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2307000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2437000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2544000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2994500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3525600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4018000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4131500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3847000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3835000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3618500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3699200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,100 +1726,104 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1493000</v>
+        <v>-2217500</v>
       </c>
       <c r="E20" s="3">
-        <v>-1958400</v>
+        <v>-1497200</v>
       </c>
       <c r="F20" s="3">
-        <v>-1302000</v>
+        <v>-1964000</v>
       </c>
       <c r="G20" s="3">
-        <v>-2834000</v>
+        <v>-1305700</v>
       </c>
       <c r="H20" s="3">
-        <v>-1843400</v>
+        <v>-2842100</v>
       </c>
       <c r="I20" s="3">
-        <v>-1726200</v>
+        <v>-1848700</v>
       </c>
       <c r="J20" s="3">
+        <v>-1731200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1848,38 +1884,41 @@
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>326500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1252700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1717300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>822400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,192 +2009,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1869500</v>
+        <v>759500</v>
       </c>
       <c r="E23" s="3">
-        <v>1524400</v>
+        <v>1874800</v>
       </c>
       <c r="F23" s="3">
-        <v>2009400</v>
+        <v>1528800</v>
       </c>
       <c r="G23" s="3">
-        <v>839800</v>
+        <v>2015200</v>
       </c>
       <c r="H23" s="3">
-        <v>1752300</v>
+        <v>842200</v>
       </c>
       <c r="I23" s="3">
-        <v>1678500</v>
+        <v>1757300</v>
       </c>
       <c r="J23" s="3">
+        <v>1683300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1798900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>88900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>596600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1232600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1681200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>174500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>172400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>224700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-841600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>350500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-378500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>560400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>780700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>474300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>922300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>566400</v>
+        <v>-795400</v>
       </c>
       <c r="E24" s="3">
-        <v>505600</v>
+        <v>568000</v>
       </c>
       <c r="F24" s="3">
-        <v>576100</v>
+        <v>507100</v>
       </c>
       <c r="G24" s="3">
-        <v>-1305300</v>
+        <v>577800</v>
       </c>
       <c r="H24" s="3">
-        <v>403600</v>
+        <v>-1309000</v>
       </c>
       <c r="I24" s="3">
-        <v>364600</v>
+        <v>404800</v>
       </c>
       <c r="J24" s="3">
+        <v>365600</v>
+      </c>
+      <c r="K24" s="3">
         <v>467600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-253700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>242300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>357600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>584000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-14000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>179600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>105800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>153800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>223000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>177600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2592800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>108900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>105300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>306800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>340400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>342600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>318600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>400600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>355700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1303100</v>
+        <v>1554900</v>
       </c>
       <c r="E26" s="3">
-        <v>1018800</v>
+        <v>1306800</v>
       </c>
       <c r="F26" s="3">
-        <v>1433300</v>
+        <v>1021700</v>
       </c>
       <c r="G26" s="3">
-        <v>2145000</v>
+        <v>1437400</v>
       </c>
       <c r="H26" s="3">
-        <v>1348700</v>
+        <v>2151200</v>
       </c>
       <c r="I26" s="3">
-        <v>1313900</v>
+        <v>1352500</v>
       </c>
       <c r="J26" s="3">
+        <v>1317700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1331300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>342600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>354300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>875000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1097100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>188500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>320700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>66500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>70900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>241600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-483800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>253600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>440300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>131800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>728200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>521700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>674900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1118600</v>
+        <v>1439600</v>
       </c>
       <c r="E27" s="3">
-        <v>828900</v>
+        <v>1121800</v>
       </c>
       <c r="F27" s="3">
-        <v>1256400</v>
+        <v>831300</v>
       </c>
       <c r="G27" s="3">
-        <v>1979000</v>
+        <v>1260000</v>
       </c>
       <c r="H27" s="3">
-        <v>1209800</v>
+        <v>1984700</v>
       </c>
       <c r="I27" s="3">
-        <v>1134900</v>
+        <v>1213200</v>
       </c>
       <c r="J27" s="3">
+        <v>1138200</v>
+      </c>
+      <c r="K27" s="3">
         <v>1150100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>225500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>208900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>732100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>960700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>83800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>188900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-84000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-46900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>117200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-502700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>233700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>310700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>47200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>725900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>178400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>670200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2578,8 +2638,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2596,12 +2656,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1493000</v>
+        <v>2217500</v>
       </c>
       <c r="E32" s="3">
-        <v>1958400</v>
+        <v>1497200</v>
       </c>
       <c r="F32" s="3">
-        <v>1302000</v>
+        <v>1964000</v>
       </c>
       <c r="G32" s="3">
-        <v>2834000</v>
+        <v>1305700</v>
       </c>
       <c r="H32" s="3">
-        <v>1843400</v>
+        <v>2842100</v>
       </c>
       <c r="I32" s="3">
-        <v>1726200</v>
+        <v>1848700</v>
       </c>
       <c r="J32" s="3">
+        <v>1731200</v>
+      </c>
+      <c r="K32" s="3">
         <v>1005800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2804600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2264700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1500200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1209300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2132400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1936700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2371600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2769800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5035000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4859500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5244400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3496500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4213500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3058100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2918500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1118600</v>
+        <v>1439600</v>
       </c>
       <c r="E33" s="3">
-        <v>828900</v>
+        <v>1121800</v>
       </c>
       <c r="F33" s="3">
-        <v>1256400</v>
+        <v>831300</v>
       </c>
       <c r="G33" s="3">
-        <v>1979000</v>
+        <v>1260000</v>
       </c>
       <c r="H33" s="3">
-        <v>1209800</v>
+        <v>1984700</v>
       </c>
       <c r="I33" s="3">
-        <v>1134900</v>
+        <v>1213200</v>
       </c>
       <c r="J33" s="3">
+        <v>1138200</v>
+      </c>
+      <c r="K33" s="3">
         <v>1150100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>225500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>208900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>732100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>960700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>83800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>188900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-84000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-46900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>117200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-502700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>233700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>310700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>47200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>725900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>178400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>670200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1118600</v>
+        <v>1439600</v>
       </c>
       <c r="E35" s="3">
-        <v>828900</v>
+        <v>1121800</v>
       </c>
       <c r="F35" s="3">
-        <v>1256400</v>
+        <v>831300</v>
       </c>
       <c r="G35" s="3">
-        <v>1979000</v>
+        <v>1260000</v>
       </c>
       <c r="H35" s="3">
-        <v>1209800</v>
+        <v>1984700</v>
       </c>
       <c r="I35" s="3">
-        <v>1134900</v>
+        <v>1213200</v>
       </c>
       <c r="J35" s="3">
+        <v>1138200</v>
+      </c>
+      <c r="K35" s="3">
         <v>1150100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>225500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>208900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>732100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>960700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>83800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>188900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-84000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-46900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>117200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-502700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>233700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>310700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>47200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>725900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>178400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>670200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,192 +3416,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>184100600</v>
+        <v>194134400</v>
       </c>
       <c r="E41" s="3">
-        <v>178575800</v>
+        <v>184626600</v>
       </c>
       <c r="F41" s="3">
-        <v>174443000</v>
+        <v>179086000</v>
       </c>
       <c r="G41" s="3">
-        <v>194102200</v>
+        <v>174941500</v>
       </c>
       <c r="H41" s="3">
-        <v>197524300</v>
+        <v>194656700</v>
       </c>
       <c r="I41" s="3">
-        <v>192121000</v>
+        <v>198088600</v>
       </c>
       <c r="J41" s="3">
+        <v>192669900</v>
+      </c>
+      <c r="K41" s="3">
         <v>181637700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>208170000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>212033000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>209767500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>190419900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>165775900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>183905500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>181344200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>132965600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>160626300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>205606000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>189379200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>224065000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>223249900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>222838000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>228478400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>553006100</v>
+        <v>528986300</v>
       </c>
       <c r="E42" s="3">
-        <v>518083200</v>
+        <v>554586100</v>
       </c>
       <c r="F42" s="3">
-        <v>513338500</v>
+        <v>519563400</v>
       </c>
       <c r="G42" s="3">
-        <v>545977400</v>
+        <v>514805100</v>
       </c>
       <c r="H42" s="3">
-        <v>658852100</v>
+        <v>547537400</v>
       </c>
       <c r="I42" s="3">
-        <v>578236600</v>
+        <v>660734600</v>
       </c>
       <c r="J42" s="3">
+        <v>579888700</v>
+      </c>
+      <c r="K42" s="3">
         <v>550086300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>549645200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>534165000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>514620700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>534342900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>545724400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>583172100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>643250700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>720305000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>647419900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>844378300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>764585900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>754124000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>709886700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>662362500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>684587600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3607,8 +3699,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3699,8 +3794,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3791,8 +3889,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3883,284 +3984,296 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1087200</v>
+        <v>1102200</v>
       </c>
       <c r="E47" s="3">
-        <v>1110000</v>
+        <v>1090300</v>
       </c>
       <c r="F47" s="3">
-        <v>1165300</v>
+        <v>1113100</v>
       </c>
       <c r="G47" s="3">
-        <v>1219500</v>
+        <v>1168600</v>
       </c>
       <c r="H47" s="3">
-        <v>1349700</v>
+        <v>1223000</v>
       </c>
       <c r="I47" s="3">
-        <v>1285700</v>
+        <v>1353600</v>
       </c>
       <c r="J47" s="3">
+        <v>1289400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1159900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1182800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1164100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1174400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1123600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>898700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>955900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1035300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>999300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1084500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1118400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1081100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1101700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1039800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>940400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>934400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>986000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>971600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6653200</v>
+        <v>6729900</v>
       </c>
       <c r="E48" s="3">
-        <v>6520900</v>
+        <v>6672200</v>
       </c>
       <c r="F48" s="3">
-        <v>6619600</v>
+        <v>6539500</v>
       </c>
       <c r="G48" s="3">
-        <v>6621800</v>
+        <v>6638500</v>
       </c>
       <c r="H48" s="3">
-        <v>6461200</v>
+        <v>6640700</v>
       </c>
       <c r="I48" s="3">
-        <v>6070600</v>
+        <v>6479600</v>
       </c>
       <c r="J48" s="3">
+        <v>6087900</v>
+      </c>
+      <c r="K48" s="3">
         <v>6035900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6001600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5725900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5689900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5773500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5534600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5979300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5253800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5238500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5755300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6297700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6274900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6506100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2863800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2775600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2788900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7956300</v>
+        <v>7972500</v>
       </c>
       <c r="E49" s="3">
-        <v>7748000</v>
+        <v>7979000</v>
       </c>
       <c r="F49" s="3">
-        <v>7690500</v>
+        <v>7770100</v>
       </c>
       <c r="G49" s="3">
-        <v>7694800</v>
+        <v>7712500</v>
       </c>
       <c r="H49" s="3">
-        <v>8027900</v>
+        <v>7716800</v>
       </c>
       <c r="I49" s="3">
-        <v>7763200</v>
+        <v>8050900</v>
       </c>
       <c r="J49" s="3">
+        <v>7785400</v>
+      </c>
+      <c r="K49" s="3">
         <v>7488700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7397900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7242200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7243100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7249400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6707500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7004800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7527300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7633100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8205700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9371200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9067700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10984700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10812900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10030400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9862200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4459,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7571100</v>
+        <v>8457800</v>
       </c>
       <c r="E52" s="3">
-        <v>7490800</v>
+        <v>7592800</v>
       </c>
       <c r="F52" s="3">
-        <v>7468100</v>
+        <v>7512200</v>
       </c>
       <c r="G52" s="3">
-        <v>7890100</v>
+        <v>7489400</v>
       </c>
       <c r="H52" s="3">
-        <v>6769300</v>
+        <v>7912700</v>
       </c>
       <c r="I52" s="3">
-        <v>6876700</v>
+        <v>6788700</v>
       </c>
       <c r="J52" s="3">
+        <v>6896400</v>
+      </c>
+      <c r="K52" s="3">
         <v>6949400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6740900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6332200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6231600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6278200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6042200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6341600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6508400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6412400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6988100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7394000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6532500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8867400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11721400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15922900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10640700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1473725100</v>
+        <v>1427947400</v>
       </c>
       <c r="E54" s="3">
-        <v>1410817900</v>
+        <v>1477935800</v>
       </c>
       <c r="F54" s="3">
-        <v>1417853000</v>
+        <v>1414848800</v>
       </c>
       <c r="G54" s="3">
-        <v>1450415000</v>
+        <v>1421904100</v>
       </c>
       <c r="H54" s="3">
-        <v>1625402700</v>
+        <v>1454559000</v>
       </c>
       <c r="I54" s="3">
-        <v>1504526100</v>
+        <v>1630046700</v>
       </c>
       <c r="J54" s="3">
+        <v>1508824700</v>
+      </c>
+      <c r="K54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,8 +4816,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4701,11 +4831,11 @@
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="3">
-        <v>3066200</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
+        <v>3075000</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
@@ -4713,24 +4843,24 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>1761700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>1735500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4749,38 +4879,41 @@
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>2940700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2523100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2478200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4871,100 +5004,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>709600</v>
+        <v>686600</v>
       </c>
       <c r="E59" s="3">
-        <v>636900</v>
+        <v>711600</v>
       </c>
       <c r="F59" s="3">
-        <v>555500</v>
+        <v>638700</v>
       </c>
       <c r="G59" s="3">
-        <v>421000</v>
+        <v>557100</v>
       </c>
       <c r="H59" s="3">
-        <v>597800</v>
+        <v>422200</v>
       </c>
       <c r="I59" s="3">
-        <v>748700</v>
+        <v>599500</v>
       </c>
       <c r="J59" s="3">
+        <v>750800</v>
+      </c>
+      <c r="K59" s="3">
         <v>768200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>650500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>855100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>921500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>815700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>572500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>714100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>836700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>711300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>760000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>851400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2138700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1063400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1116700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>985800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1012400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5055,192 +5194,201 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>218370400</v>
+        <v>221326100</v>
       </c>
       <c r="E61" s="3">
-        <v>219150500</v>
+        <v>218994300</v>
       </c>
       <c r="F61" s="3">
-        <v>227021100</v>
+        <v>219776600</v>
       </c>
       <c r="G61" s="3">
-        <v>202525000</v>
+        <v>227669700</v>
       </c>
       <c r="H61" s="3">
-        <v>221001500</v>
+        <v>203103700</v>
       </c>
       <c r="I61" s="3">
-        <v>221932400</v>
+        <v>221632900</v>
       </c>
       <c r="J61" s="3">
+        <v>222566500</v>
+      </c>
+      <c r="K61" s="3">
         <v>210513900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>220593800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>224408700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>214884000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>210056400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>196553600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>216575500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>227441600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>217812200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>220428000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>255682400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>238475100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>267994300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>190280100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>179290500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>183304500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3716100</v>
+        <v>3257800</v>
       </c>
       <c r="E62" s="3">
-        <v>3735700</v>
+        <v>3726700</v>
       </c>
       <c r="F62" s="3">
-        <v>3667300</v>
+        <v>3746300</v>
       </c>
       <c r="G62" s="3">
-        <v>3588100</v>
+        <v>3677800</v>
       </c>
       <c r="H62" s="3">
-        <v>3517600</v>
+        <v>3598300</v>
       </c>
       <c r="I62" s="3">
-        <v>3711800</v>
+        <v>3527600</v>
       </c>
       <c r="J62" s="3">
+        <v>3722400</v>
+      </c>
+      <c r="K62" s="3">
         <v>4141400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3679400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3266200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3242800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3485100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12807600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3260000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3497500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3710200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3697200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3912600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3751500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4158000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5281600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9456700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7174300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1395478200</v>
+        <v>1348456200</v>
       </c>
       <c r="E66" s="3">
-        <v>1333792700</v>
+        <v>1399465300</v>
       </c>
       <c r="F66" s="3">
-        <v>1340186600</v>
+        <v>1337603500</v>
       </c>
       <c r="G66" s="3">
-        <v>1373882300</v>
+        <v>1344015700</v>
       </c>
       <c r="H66" s="3">
-        <v>1550485600</v>
+        <v>1377807700</v>
       </c>
       <c r="I66" s="3">
-        <v>1431705200</v>
+        <v>1554915600</v>
       </c>
       <c r="J66" s="3">
+        <v>1435795800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>21886600</v>
+        <v>23193900</v>
       </c>
       <c r="E72" s="3">
-        <v>20669300</v>
+        <v>21949200</v>
       </c>
       <c r="F72" s="3">
-        <v>20925300</v>
+        <v>20728300</v>
       </c>
       <c r="G72" s="3">
-        <v>19313000</v>
+        <v>20985100</v>
       </c>
       <c r="H72" s="3">
-        <v>17076800</v>
+        <v>19368200</v>
       </c>
       <c r="I72" s="3">
-        <v>15676100</v>
+        <v>17125600</v>
       </c>
       <c r="J72" s="3">
+        <v>15720900</v>
+      </c>
+      <c r="K72" s="3">
         <v>15034800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13667200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13118800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12484400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11771300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9988000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9959700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10335300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10680000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11258500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14121700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14850900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19841400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19771000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19008600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18649500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>78246900</v>
+        <v>79491100</v>
       </c>
       <c r="E76" s="3">
-        <v>77025200</v>
+        <v>78470500</v>
       </c>
       <c r="F76" s="3">
-        <v>77666500</v>
+        <v>77245300</v>
       </c>
       <c r="G76" s="3">
-        <v>76532600</v>
+        <v>77888400</v>
       </c>
       <c r="H76" s="3">
-        <v>74917100</v>
+        <v>76751300</v>
       </c>
       <c r="I76" s="3">
-        <v>72820900</v>
+        <v>75131100</v>
       </c>
       <c r="J76" s="3">
+        <v>73028900</v>
+      </c>
+      <c r="K76" s="3">
         <v>72670000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71910500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>69245700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>67327900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>65506100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>60451400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>62888400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66729900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>67336400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70654000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>77200100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>74603800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>80850000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>79454200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>74489400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>73930500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1118600</v>
+        <v>1439600</v>
       </c>
       <c r="E81" s="3">
-        <v>828900</v>
+        <v>1121800</v>
       </c>
       <c r="F81" s="3">
-        <v>1256400</v>
+        <v>831300</v>
       </c>
       <c r="G81" s="3">
-        <v>1979000</v>
+        <v>1260000</v>
       </c>
       <c r="H81" s="3">
-        <v>1209800</v>
+        <v>1984700</v>
       </c>
       <c r="I81" s="3">
-        <v>1134900</v>
+        <v>1213200</v>
       </c>
       <c r="J81" s="3">
+        <v>1138200</v>
+      </c>
+      <c r="K81" s="3">
         <v>1150100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>225500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>208900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>732100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>960700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>83800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>188900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-84000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-46900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>117200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-502700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>233700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>310700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>47200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>725900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>178400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>670200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,37 +6981,38 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
@@ -6822,8 +7020,8 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -6843,41 +7041,44 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>705000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>692300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>936600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>348100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>732700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>366900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>544200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>814600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,37 +7549,40 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>5</v>
@@ -7374,8 +7590,8 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P89" s="3">
         <v>0</v>
@@ -7395,41 +7611,44 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,46 +7681,47 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-244000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-178000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-154000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-183000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-301000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-249000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-331000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-181000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7521,41 +7741,44 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-153800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-154000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-109800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AE91" s="3">
         <v>-340400</v>
       </c>
       <c r="AF91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,37 +7964,40 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
@@ -7776,8 +8005,8 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -7797,41 +8026,44 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-923800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5880900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>252400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,8 +8096,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7945,19 +8178,22 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,37 +8474,40 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
@@ -8270,8 +8515,8 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -8291,70 +8536,73 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-132500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-332300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>911100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
@@ -8362,8 +8610,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8383,70 +8631,73 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>1113100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>875000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1412000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>430800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
@@ -8454,8 +8705,8 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
@@ -8475,37 +8726,40 @@
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,217 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>13361900</v>
+        <v>13628700</v>
       </c>
       <c r="E8" s="3">
-        <v>12432600</v>
+        <v>13271000</v>
       </c>
       <c r="F8" s="3">
-        <v>11598100</v>
+        <v>12348100</v>
       </c>
       <c r="G8" s="3">
-        <v>10565500</v>
+        <v>11519200</v>
       </c>
       <c r="H8" s="3">
-        <v>8942000</v>
+        <v>10493600</v>
       </c>
       <c r="I8" s="3">
-        <v>6975800</v>
+        <v>8881200</v>
       </c>
       <c r="J8" s="3">
+        <v>6928400</v>
+      </c>
+      <c r="K8" s="3">
         <v>5707100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4801100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4626900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4467000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4179100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4479600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3846000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4143300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4898200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5964000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6438300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7751700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8073600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7778900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7110400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6720900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -960,8 +966,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1064,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,8 +1394,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1470,8 +1492,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10384800</v>
+        <v>10721600</v>
       </c>
       <c r="E17" s="3">
-        <v>9060600</v>
+        <v>10314200</v>
       </c>
       <c r="F17" s="3">
-        <v>8105300</v>
+        <v>8999000</v>
       </c>
       <c r="G17" s="3">
-        <v>7244600</v>
+        <v>8050100</v>
       </c>
       <c r="H17" s="3">
-        <v>5257700</v>
+        <v>7195300</v>
       </c>
       <c r="I17" s="3">
-        <v>3369800</v>
+        <v>5221900</v>
       </c>
       <c r="J17" s="3">
+        <v>3346900</v>
+      </c>
+      <c r="K17" s="3">
         <v>2292600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1996400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1733500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1605700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1446300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1589100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1539000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1706300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2354200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2969500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2912700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3733800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3942100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3931900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3275500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3102400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2977000</v>
+        <v>2907100</v>
       </c>
       <c r="E18" s="3">
-        <v>3372000</v>
+        <v>2956800</v>
       </c>
       <c r="F18" s="3">
-        <v>3492800</v>
+        <v>3349100</v>
       </c>
       <c r="G18" s="3">
-        <v>3320900</v>
+        <v>3469000</v>
       </c>
       <c r="H18" s="3">
-        <v>3684300</v>
+        <v>3298300</v>
       </c>
       <c r="I18" s="3">
-        <v>3606000</v>
+        <v>3659300</v>
       </c>
       <c r="J18" s="3">
+        <v>3581400</v>
+      </c>
+      <c r="K18" s="3">
         <v>3414500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2804700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2893500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2861300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2732800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2890500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2307000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2437000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2544000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2994500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3525600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4018000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4131500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3847000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3835000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3618500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,103 +1759,107 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2217500</v>
+        <v>-706800</v>
       </c>
       <c r="E20" s="3">
-        <v>-1497200</v>
+        <v>-2202500</v>
       </c>
       <c r="F20" s="3">
-        <v>-1964000</v>
+        <v>-1487000</v>
       </c>
       <c r="G20" s="3">
-        <v>-1305700</v>
+        <v>-1950700</v>
       </c>
       <c r="H20" s="3">
-        <v>-2842100</v>
+        <v>-1296800</v>
       </c>
       <c r="I20" s="3">
-        <v>-1848700</v>
+        <v>-2822800</v>
       </c>
       <c r="J20" s="3">
+        <v>-1836100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1887,38 +1923,41 @@
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>326500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1252700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>822400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2012,198 +2051,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>759500</v>
+        <v>2200300</v>
       </c>
       <c r="E23" s="3">
-        <v>1874800</v>
+        <v>754300</v>
       </c>
       <c r="F23" s="3">
-        <v>1528800</v>
+        <v>1862000</v>
       </c>
       <c r="G23" s="3">
-        <v>2015200</v>
+        <v>1518400</v>
       </c>
       <c r="H23" s="3">
-        <v>842200</v>
+        <v>2001500</v>
       </c>
       <c r="I23" s="3">
-        <v>1757300</v>
+        <v>836500</v>
       </c>
       <c r="J23" s="3">
+        <v>1745300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1683300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1798900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>88900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>596600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1232600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1681200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>174500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>500300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>172400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>224700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-841600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>350500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-378500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>560400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>780700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>474300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>922300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-795400</v>
+        <v>632200</v>
       </c>
       <c r="E24" s="3">
-        <v>568000</v>
+        <v>-790000</v>
       </c>
       <c r="F24" s="3">
-        <v>507100</v>
+        <v>564100</v>
       </c>
       <c r="G24" s="3">
-        <v>577800</v>
+        <v>503600</v>
       </c>
       <c r="H24" s="3">
-        <v>-1309000</v>
+        <v>573900</v>
       </c>
       <c r="I24" s="3">
-        <v>404800</v>
+        <v>-1300100</v>
       </c>
       <c r="J24" s="3">
+        <v>402000</v>
+      </c>
+      <c r="K24" s="3">
         <v>365600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>467600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-253700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>242300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>357600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>584000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>179600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>105800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>153800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>223000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>177600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2592800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>108900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>105300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>306800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>340400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>342600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>318600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>400600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>355700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1554900</v>
+        <v>1568100</v>
       </c>
       <c r="E26" s="3">
-        <v>1306800</v>
+        <v>1544300</v>
       </c>
       <c r="F26" s="3">
-        <v>1021700</v>
+        <v>1297900</v>
       </c>
       <c r="G26" s="3">
-        <v>1437400</v>
+        <v>1014800</v>
       </c>
       <c r="H26" s="3">
-        <v>2151200</v>
+        <v>1427600</v>
       </c>
       <c r="I26" s="3">
-        <v>1352500</v>
+        <v>2136500</v>
       </c>
       <c r="J26" s="3">
+        <v>1343300</v>
+      </c>
+      <c r="K26" s="3">
         <v>1317700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1331300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>342600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>354300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>875000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1097100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>188500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>320700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>66500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>70900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>241600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-483800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>253600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>440300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>131800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>728200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>521700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>674900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1439600</v>
+        <v>1377900</v>
       </c>
       <c r="E27" s="3">
-        <v>1121800</v>
+        <v>1429800</v>
       </c>
       <c r="F27" s="3">
-        <v>831300</v>
+        <v>1114200</v>
       </c>
       <c r="G27" s="3">
-        <v>1260000</v>
+        <v>825700</v>
       </c>
       <c r="H27" s="3">
-        <v>1984700</v>
+        <v>1251500</v>
       </c>
       <c r="I27" s="3">
-        <v>1213200</v>
+        <v>1971200</v>
       </c>
       <c r="J27" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="K27" s="3">
         <v>1138200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1150100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>225500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>208900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>732100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>960700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>83800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>188900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-84000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-46900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>117200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-502700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>233700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>310700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>47200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>725900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>178400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>670200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2641,8 +2701,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2659,12 +2719,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2217500</v>
+        <v>706800</v>
       </c>
       <c r="E32" s="3">
-        <v>1497200</v>
+        <v>2202500</v>
       </c>
       <c r="F32" s="3">
-        <v>1964000</v>
+        <v>1487000</v>
       </c>
       <c r="G32" s="3">
-        <v>1305700</v>
+        <v>1950700</v>
       </c>
       <c r="H32" s="3">
-        <v>2842100</v>
+        <v>1296800</v>
       </c>
       <c r="I32" s="3">
-        <v>1848700</v>
+        <v>2822800</v>
       </c>
       <c r="J32" s="3">
+        <v>1836100</v>
+      </c>
+      <c r="K32" s="3">
         <v>1731200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1005800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2804600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2264700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1500200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1209300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2132400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1936700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2371600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2769800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5035000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4859500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5244400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3496500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4213500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3058100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1439600</v>
+        <v>1377900</v>
       </c>
       <c r="E33" s="3">
-        <v>1121800</v>
+        <v>1429800</v>
       </c>
       <c r="F33" s="3">
-        <v>831300</v>
+        <v>1114200</v>
       </c>
       <c r="G33" s="3">
-        <v>1260000</v>
+        <v>825700</v>
       </c>
       <c r="H33" s="3">
-        <v>1984700</v>
+        <v>1251500</v>
       </c>
       <c r="I33" s="3">
-        <v>1213200</v>
+        <v>1971200</v>
       </c>
       <c r="J33" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="K33" s="3">
         <v>1138200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1150100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>225500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>208900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>732100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>960700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>83800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>188900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-84000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-46900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>117200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-502700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>233700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>310700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>47200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>725900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>178400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>670200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1439600</v>
+        <v>1377900</v>
       </c>
       <c r="E35" s="3">
-        <v>1121800</v>
+        <v>1429800</v>
       </c>
       <c r="F35" s="3">
-        <v>831300</v>
+        <v>1114200</v>
       </c>
       <c r="G35" s="3">
-        <v>1260000</v>
+        <v>825700</v>
       </c>
       <c r="H35" s="3">
-        <v>1984700</v>
+        <v>1251500</v>
       </c>
       <c r="I35" s="3">
-        <v>1213200</v>
+        <v>1971200</v>
       </c>
       <c r="J35" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="K35" s="3">
         <v>1138200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1150100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>225500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>208900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>732100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>960700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>83800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>188900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-84000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-46900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>117200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-502700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>233700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>310700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>47200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>725900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>178400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>670200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,198 +3502,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>194134400</v>
+        <v>160200800</v>
       </c>
       <c r="E41" s="3">
-        <v>184626600</v>
+        <v>192814200</v>
       </c>
       <c r="F41" s="3">
-        <v>179086000</v>
+        <v>183371000</v>
       </c>
       <c r="G41" s="3">
-        <v>174941500</v>
+        <v>177868100</v>
       </c>
       <c r="H41" s="3">
-        <v>194656700</v>
+        <v>173751700</v>
       </c>
       <c r="I41" s="3">
-        <v>198088600</v>
+        <v>193332900</v>
       </c>
       <c r="J41" s="3">
+        <v>196741400</v>
+      </c>
+      <c r="K41" s="3">
         <v>192669900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>181637700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>208170000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>212033000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>209767500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>190419900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>165775900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>183905500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>181344200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>132965600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>160626300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>205606000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>189379200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>224065000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>223249900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>222838000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>528986300</v>
+        <v>534525000</v>
       </c>
       <c r="E42" s="3">
-        <v>554586100</v>
+        <v>525388800</v>
       </c>
       <c r="F42" s="3">
-        <v>519563400</v>
+        <v>550814400</v>
       </c>
       <c r="G42" s="3">
-        <v>514805100</v>
+        <v>516029900</v>
       </c>
       <c r="H42" s="3">
-        <v>547537400</v>
+        <v>511304000</v>
       </c>
       <c r="I42" s="3">
-        <v>660734600</v>
+        <v>543813600</v>
       </c>
       <c r="J42" s="3">
+        <v>656241000</v>
+      </c>
+      <c r="K42" s="3">
         <v>579888700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>550086300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>549645200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>534165000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>514620700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>534342900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>545724400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>583172100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>643250700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>720305000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>647419900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>844378300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>764585900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>754124000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>709886700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>662362500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3702,8 +3794,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3797,8 +3892,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3892,8 +3990,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3987,293 +4088,305 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1102200</v>
+        <v>1109900</v>
       </c>
       <c r="E47" s="3">
-        <v>1090300</v>
+        <v>1094700</v>
       </c>
       <c r="F47" s="3">
-        <v>1113100</v>
+        <v>1082900</v>
       </c>
       <c r="G47" s="3">
-        <v>1168600</v>
+        <v>1105600</v>
       </c>
       <c r="H47" s="3">
-        <v>1223000</v>
+        <v>1160700</v>
       </c>
       <c r="I47" s="3">
-        <v>1353600</v>
+        <v>1214700</v>
       </c>
       <c r="J47" s="3">
+        <v>1344400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1289400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1159900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1182800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1164100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1174400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1123600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>898700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>955900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1035300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>999300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1084500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1118400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1081100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1101700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1039800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>940400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>934400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>986000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>971600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6729900</v>
+        <v>6758700</v>
       </c>
       <c r="E48" s="3">
-        <v>6672200</v>
+        <v>6684100</v>
       </c>
       <c r="F48" s="3">
-        <v>6539500</v>
+        <v>6626900</v>
       </c>
       <c r="G48" s="3">
-        <v>6638500</v>
+        <v>6495000</v>
       </c>
       <c r="H48" s="3">
-        <v>6640700</v>
+        <v>6593400</v>
       </c>
       <c r="I48" s="3">
-        <v>6479600</v>
+        <v>6595500</v>
       </c>
       <c r="J48" s="3">
+        <v>6435600</v>
+      </c>
+      <c r="K48" s="3">
         <v>6087900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6035900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6001600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5725900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5689900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5773500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5534600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5979300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5253800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5238500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5755300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6297700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6274900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6506100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2863800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2775600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7972500</v>
+        <v>8063100</v>
       </c>
       <c r="E49" s="3">
-        <v>7979000</v>
+        <v>7918300</v>
       </c>
       <c r="F49" s="3">
-        <v>7770100</v>
+        <v>7924800</v>
       </c>
       <c r="G49" s="3">
-        <v>7712500</v>
+        <v>7717300</v>
       </c>
       <c r="H49" s="3">
-        <v>7716800</v>
+        <v>7660000</v>
       </c>
       <c r="I49" s="3">
-        <v>8050900</v>
+        <v>7664300</v>
       </c>
       <c r="J49" s="3">
+        <v>7996100</v>
+      </c>
+      <c r="K49" s="3">
         <v>7785400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7488700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7397900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7242200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7243100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7249400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6707500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7004800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7527300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7633100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8205700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9371200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9067700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10984700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10812900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10030400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,103 +4578,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8457800</v>
+        <v>8410000</v>
       </c>
       <c r="E52" s="3">
-        <v>7592800</v>
+        <v>8400300</v>
       </c>
       <c r="F52" s="3">
-        <v>7512200</v>
+        <v>7541100</v>
       </c>
       <c r="G52" s="3">
-        <v>7489400</v>
+        <v>7461200</v>
       </c>
       <c r="H52" s="3">
-        <v>7912700</v>
+        <v>7438500</v>
       </c>
       <c r="I52" s="3">
-        <v>6788700</v>
+        <v>7858900</v>
       </c>
       <c r="J52" s="3">
+        <v>6742500</v>
+      </c>
+      <c r="K52" s="3">
         <v>6896400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6949400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6740900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6332200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6231600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6278200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6042200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6341600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6508400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6412400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6988100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7394000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6532500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8867400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11721400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15922900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1427947400</v>
+        <v>1438179300</v>
       </c>
       <c r="E54" s="3">
-        <v>1477935800</v>
+        <v>1418236100</v>
       </c>
       <c r="F54" s="3">
-        <v>1414848800</v>
+        <v>1467884600</v>
       </c>
       <c r="G54" s="3">
-        <v>1421904100</v>
+        <v>1405226600</v>
       </c>
       <c r="H54" s="3">
-        <v>1454559000</v>
+        <v>1412233900</v>
       </c>
       <c r="I54" s="3">
-        <v>1630046700</v>
+        <v>1444666800</v>
       </c>
       <c r="J54" s="3">
+        <v>1618961000</v>
+      </c>
+      <c r="K54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,8 +4946,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4834,11 +4964,11 @@
       <c r="G57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H57" s="3">
-        <v>3075000</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
+        <v>3054100</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -4846,24 +4976,24 @@
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>1761700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1735500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4882,38 +5012,41 @@
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>2940700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2523100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5007,103 +5140,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>686600</v>
+        <v>746800</v>
       </c>
       <c r="E59" s="3">
-        <v>711600</v>
+        <v>681900</v>
       </c>
       <c r="F59" s="3">
-        <v>638700</v>
+        <v>706800</v>
       </c>
       <c r="G59" s="3">
-        <v>557100</v>
+        <v>634400</v>
       </c>
       <c r="H59" s="3">
-        <v>422200</v>
+        <v>553300</v>
       </c>
       <c r="I59" s="3">
-        <v>599500</v>
+        <v>419300</v>
       </c>
       <c r="J59" s="3">
+        <v>595500</v>
+      </c>
+      <c r="K59" s="3">
         <v>750800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>768200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>650500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>855100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>921500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>815700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>572500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>714100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>836700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>711300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>760000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>851400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2138700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1063400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1116700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>985800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5197,198 +5336,207 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>221326100</v>
+        <v>206418000</v>
       </c>
       <c r="E61" s="3">
-        <v>218994300</v>
+        <v>219820900</v>
       </c>
       <c r="F61" s="3">
-        <v>219776600</v>
+        <v>217504900</v>
       </c>
       <c r="G61" s="3">
-        <v>227669700</v>
+        <v>218281900</v>
       </c>
       <c r="H61" s="3">
-        <v>203103700</v>
+        <v>226121300</v>
       </c>
       <c r="I61" s="3">
-        <v>221632900</v>
+        <v>201722400</v>
       </c>
       <c r="J61" s="3">
+        <v>220125600</v>
+      </c>
+      <c r="K61" s="3">
         <v>222566500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>210513900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>220593800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>224408700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>214884000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>210056400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>196553600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>216575500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>227441600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>217812200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>220428000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>255682400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>238475100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>267994300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>190280100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>179290500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3257800</v>
+        <v>3346900</v>
       </c>
       <c r="E62" s="3">
-        <v>3726700</v>
+        <v>3235600</v>
       </c>
       <c r="F62" s="3">
-        <v>3746300</v>
+        <v>3701400</v>
       </c>
       <c r="G62" s="3">
-        <v>3677800</v>
+        <v>3720900</v>
       </c>
       <c r="H62" s="3">
-        <v>3598300</v>
+        <v>3652800</v>
       </c>
       <c r="I62" s="3">
-        <v>3527600</v>
+        <v>3573900</v>
       </c>
       <c r="J62" s="3">
+        <v>3503600</v>
+      </c>
+      <c r="K62" s="3">
         <v>3722400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4141400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3679400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3266200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3242800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3485100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12807600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3260000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3497500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3710200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3697200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3912600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3751500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4158000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5281600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9456700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1348456200</v>
+        <v>1358123300</v>
       </c>
       <c r="E66" s="3">
-        <v>1399465300</v>
+        <v>1339285600</v>
       </c>
       <c r="F66" s="3">
-        <v>1337603500</v>
+        <v>1389947700</v>
       </c>
       <c r="G66" s="3">
-        <v>1344015700</v>
+        <v>1328506700</v>
       </c>
       <c r="H66" s="3">
-        <v>1377807700</v>
+        <v>1334875200</v>
       </c>
       <c r="I66" s="3">
-        <v>1554915600</v>
+        <v>1368437500</v>
       </c>
       <c r="J66" s="3">
+        <v>1544340800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>23193900</v>
+        <v>24641000</v>
       </c>
       <c r="E72" s="3">
-        <v>21949200</v>
+        <v>23036200</v>
       </c>
       <c r="F72" s="3">
-        <v>20728300</v>
+        <v>21799900</v>
       </c>
       <c r="G72" s="3">
-        <v>20985100</v>
+        <v>20587300</v>
       </c>
       <c r="H72" s="3">
-        <v>19368200</v>
+        <v>20842400</v>
       </c>
       <c r="I72" s="3">
-        <v>17125600</v>
+        <v>19236500</v>
       </c>
       <c r="J72" s="3">
+        <v>17009100</v>
+      </c>
+      <c r="K72" s="3">
         <v>15720900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15034800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13667200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13118800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12484400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11771300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9988000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9959700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10335300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10680000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11258500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14121700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14850900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19841400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19771000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19008600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>79491100</v>
+        <v>80056100</v>
       </c>
       <c r="E76" s="3">
-        <v>78470500</v>
+        <v>78950500</v>
       </c>
       <c r="F76" s="3">
-        <v>77245300</v>
+        <v>77936800</v>
       </c>
       <c r="G76" s="3">
-        <v>77888400</v>
+        <v>76720000</v>
       </c>
       <c r="H76" s="3">
-        <v>76751300</v>
+        <v>77358700</v>
       </c>
       <c r="I76" s="3">
-        <v>75131100</v>
+        <v>76229300</v>
       </c>
       <c r="J76" s="3">
+        <v>74620200</v>
+      </c>
+      <c r="K76" s="3">
         <v>73028900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72670000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71910500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>69245700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>67327900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>65506100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>60451400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62888400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>66729900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>67336400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>70654000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>77200100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74603800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>80850000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>79454200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>74489400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1439600</v>
+        <v>1377900</v>
       </c>
       <c r="E81" s="3">
-        <v>1121800</v>
+        <v>1429800</v>
       </c>
       <c r="F81" s="3">
-        <v>831300</v>
+        <v>1114200</v>
       </c>
       <c r="G81" s="3">
-        <v>1260000</v>
+        <v>825700</v>
       </c>
       <c r="H81" s="3">
-        <v>1984700</v>
+        <v>1251500</v>
       </c>
       <c r="I81" s="3">
-        <v>1213200</v>
+        <v>1971200</v>
       </c>
       <c r="J81" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="K81" s="3">
         <v>1138200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1150100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>225500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>208900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>732100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>960700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>83800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>188900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-84000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-46900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>117200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-502700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>233700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>310700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>47200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>725900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>178400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>670200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,40 +7179,41 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
@@ -7023,8 +7221,8 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -7044,41 +7242,44 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>705000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>692300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>936600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>348100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>732700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>366900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>544200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>814600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,40 +7765,43 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>5</v>
@@ -7593,8 +7809,8 @@
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -7614,41 +7830,44 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,8 +7901,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7706,25 +7926,25 @@
         <v>-249000</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-331000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-181000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7744,41 +7964,44 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-153800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-154000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AF91" s="3">
         <v>-340400</v>
       </c>
       <c r="AG91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,40 +8193,43 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
@@ -8008,8 +8237,8 @@
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -8029,41 +8258,44 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-923800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>252400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,8 +8329,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8181,19 +8414,22 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,40 +8719,43 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
@@ -8518,8 +8763,8 @@
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -8539,73 +8784,76 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-132500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-332300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>911100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
@@ -8613,8 +8861,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8634,73 +8882,76 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1113100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>875000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>430800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>5</v>
@@ -8708,8 +8959,8 @@
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -8729,37 +8980,40 @@
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>13628700</v>
+        <v>14012200</v>
       </c>
       <c r="E8" s="3">
-        <v>13271000</v>
+        <v>13967900</v>
       </c>
       <c r="F8" s="3">
-        <v>12348100</v>
+        <v>13601300</v>
       </c>
       <c r="G8" s="3">
-        <v>11519200</v>
+        <v>12655400</v>
       </c>
       <c r="H8" s="3">
-        <v>10493600</v>
+        <v>11805900</v>
       </c>
       <c r="I8" s="3">
-        <v>8881200</v>
+        <v>10754800</v>
       </c>
       <c r="J8" s="3">
+        <v>9102300</v>
+      </c>
+      <c r="K8" s="3">
         <v>6928400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5707100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4801100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4626900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4467000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4179100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4479600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3846000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4143300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4898200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5964000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6438300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7751700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8073600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7778900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7110400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -969,8 +975,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,8 +1076,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1416,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,8 +1517,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10721600</v>
+        <v>11191200</v>
       </c>
       <c r="E17" s="3">
-        <v>10314200</v>
+        <v>10988500</v>
       </c>
       <c r="F17" s="3">
-        <v>8999000</v>
+        <v>10570900</v>
       </c>
       <c r="G17" s="3">
-        <v>8050100</v>
+        <v>9223000</v>
       </c>
       <c r="H17" s="3">
-        <v>7195300</v>
+        <v>8250500</v>
       </c>
       <c r="I17" s="3">
-        <v>5221900</v>
+        <v>7374400</v>
       </c>
       <c r="J17" s="3">
+        <v>5351900</v>
+      </c>
+      <c r="K17" s="3">
         <v>3346900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2292600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1996400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1733500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1605700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1446300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1589100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1539000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1706300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2354200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2969500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2912700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3733800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3942100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3931900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3275500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2907100</v>
+        <v>2821100</v>
       </c>
       <c r="E18" s="3">
-        <v>2956800</v>
+        <v>2979400</v>
       </c>
       <c r="F18" s="3">
-        <v>3349100</v>
+        <v>3030400</v>
       </c>
       <c r="G18" s="3">
-        <v>3469000</v>
+        <v>3432500</v>
       </c>
       <c r="H18" s="3">
-        <v>3298300</v>
+        <v>3555400</v>
       </c>
       <c r="I18" s="3">
-        <v>3659300</v>
+        <v>3380400</v>
       </c>
       <c r="J18" s="3">
+        <v>3750300</v>
+      </c>
+      <c r="K18" s="3">
         <v>3581400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3414500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2804700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2893500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2861300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2732800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2890500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2307000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2437000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2544000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2994500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3525600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4018000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4131500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3847000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3835000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,106 +1792,110 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-706800</v>
+        <v>-2365800</v>
       </c>
       <c r="E20" s="3">
-        <v>-2202500</v>
+        <v>-724400</v>
       </c>
       <c r="F20" s="3">
-        <v>-1487000</v>
+        <v>-2257300</v>
       </c>
       <c r="G20" s="3">
-        <v>-1950700</v>
+        <v>-1524100</v>
       </c>
       <c r="H20" s="3">
-        <v>-1296800</v>
+        <v>-1999200</v>
       </c>
       <c r="I20" s="3">
-        <v>-2822800</v>
+        <v>-1329100</v>
       </c>
       <c r="J20" s="3">
+        <v>-2893100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1926,38 +1962,41 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>326500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>822400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2054,204 +2093,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2200300</v>
+        <v>455200</v>
       </c>
       <c r="E23" s="3">
-        <v>754300</v>
+        <v>2255100</v>
       </c>
       <c r="F23" s="3">
-        <v>1862000</v>
+        <v>773100</v>
       </c>
       <c r="G23" s="3">
-        <v>1518400</v>
+        <v>1908400</v>
       </c>
       <c r="H23" s="3">
-        <v>2001500</v>
+        <v>1556200</v>
       </c>
       <c r="I23" s="3">
-        <v>836500</v>
+        <v>2051300</v>
       </c>
       <c r="J23" s="3">
+        <v>857300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1745300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1683300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1798900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>88900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>596600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1232600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1681200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>174500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>500300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>172400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>224700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-841600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>350500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-378500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>560400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>780700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>474300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>922300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>632200</v>
+        <v>396500</v>
       </c>
       <c r="E24" s="3">
-        <v>-790000</v>
+        <v>647900</v>
       </c>
       <c r="F24" s="3">
-        <v>564100</v>
+        <v>-809700</v>
       </c>
       <c r="G24" s="3">
-        <v>503600</v>
+        <v>578200</v>
       </c>
       <c r="H24" s="3">
-        <v>573900</v>
+        <v>516100</v>
       </c>
       <c r="I24" s="3">
-        <v>-1300100</v>
+        <v>588100</v>
       </c>
       <c r="J24" s="3">
+        <v>-1332400</v>
+      </c>
+      <c r="K24" s="3">
         <v>402000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>365600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>467600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-253700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>242300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>357600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>584000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-14000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>179600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>105800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>153800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>223000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>177600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2592800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>108900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>105300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>306800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>340400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>342600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>318600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>400600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>355700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1568100</v>
+        <v>58700</v>
       </c>
       <c r="E26" s="3">
-        <v>1544300</v>
+        <v>1607100</v>
       </c>
       <c r="F26" s="3">
-        <v>1297900</v>
+        <v>1582800</v>
       </c>
       <c r="G26" s="3">
-        <v>1014800</v>
+        <v>1330200</v>
       </c>
       <c r="H26" s="3">
-        <v>1427600</v>
+        <v>1040000</v>
       </c>
       <c r="I26" s="3">
-        <v>2136500</v>
+        <v>1463100</v>
       </c>
       <c r="J26" s="3">
+        <v>2189700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1343300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1317700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1331300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>342600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>354300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>875000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1097100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>188500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>320700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>66500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>70900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>241600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-483800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>253600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>440300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>131800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>728200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>521700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>674900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1377900</v>
+        <v>-158400</v>
       </c>
       <c r="E27" s="3">
-        <v>1429800</v>
+        <v>1412200</v>
       </c>
       <c r="F27" s="3">
-        <v>1114200</v>
+        <v>1465400</v>
       </c>
       <c r="G27" s="3">
-        <v>825700</v>
+        <v>1141900</v>
       </c>
       <c r="H27" s="3">
-        <v>1251500</v>
+        <v>846200</v>
       </c>
       <c r="I27" s="3">
-        <v>1971200</v>
+        <v>1282600</v>
       </c>
       <c r="J27" s="3">
+        <v>2020300</v>
+      </c>
+      <c r="K27" s="3">
         <v>1205000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1138200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1150100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>225500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>208900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>732100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>960700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>83800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>188900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-84000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-46900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>117200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-502700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>233700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>310700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>47200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>725900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>178400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>670200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2704,8 +2764,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2722,12 +2782,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>706800</v>
+        <v>2365800</v>
       </c>
       <c r="E32" s="3">
-        <v>2202500</v>
+        <v>724400</v>
       </c>
       <c r="F32" s="3">
-        <v>1487000</v>
+        <v>2257300</v>
       </c>
       <c r="G32" s="3">
-        <v>1950700</v>
+        <v>1524100</v>
       </c>
       <c r="H32" s="3">
-        <v>1296800</v>
+        <v>1999200</v>
       </c>
       <c r="I32" s="3">
-        <v>2822800</v>
+        <v>1329100</v>
       </c>
       <c r="J32" s="3">
+        <v>2893100</v>
+      </c>
+      <c r="K32" s="3">
         <v>1836100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1731200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1005800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2804600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2264700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1500200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1209300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2132400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1936700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2371600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2769800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5035000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4859500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5244400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3496500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4213500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1377900</v>
+        <v>-158400</v>
       </c>
       <c r="E33" s="3">
-        <v>1429800</v>
+        <v>1412200</v>
       </c>
       <c r="F33" s="3">
-        <v>1114200</v>
+        <v>1465400</v>
       </c>
       <c r="G33" s="3">
-        <v>825700</v>
+        <v>1141900</v>
       </c>
       <c r="H33" s="3">
-        <v>1251500</v>
+        <v>846200</v>
       </c>
       <c r="I33" s="3">
-        <v>1971200</v>
+        <v>1282600</v>
       </c>
       <c r="J33" s="3">
+        <v>2020300</v>
+      </c>
+      <c r="K33" s="3">
         <v>1205000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1138200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1150100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>225500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>208900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>732100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>960700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>83800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>188900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-84000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-46900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>117200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-502700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>233700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>310700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>47200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>725900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>178400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>670200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1377900</v>
+        <v>-158400</v>
       </c>
       <c r="E35" s="3">
-        <v>1429800</v>
+        <v>1412200</v>
       </c>
       <c r="F35" s="3">
-        <v>1114200</v>
+        <v>1465400</v>
       </c>
       <c r="G35" s="3">
-        <v>825700</v>
+        <v>1141900</v>
       </c>
       <c r="H35" s="3">
-        <v>1251500</v>
+        <v>846200</v>
       </c>
       <c r="I35" s="3">
-        <v>1971200</v>
+        <v>1282600</v>
       </c>
       <c r="J35" s="3">
+        <v>2020300</v>
+      </c>
+      <c r="K35" s="3">
         <v>1205000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1138200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1150100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>225500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>208900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>732100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>960700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>83800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>188900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-84000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-46900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>117200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-502700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>233700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>310700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>47200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>725900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>178400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>670200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,204 +3588,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>160200800</v>
+        <v>164617100</v>
       </c>
       <c r="E41" s="3">
-        <v>192814200</v>
+        <v>164188400</v>
       </c>
       <c r="F41" s="3">
-        <v>183371000</v>
+        <v>197613600</v>
       </c>
       <c r="G41" s="3">
-        <v>177868100</v>
+        <v>187935400</v>
       </c>
       <c r="H41" s="3">
-        <v>173751700</v>
+        <v>182295500</v>
       </c>
       <c r="I41" s="3">
-        <v>193332900</v>
+        <v>178076600</v>
       </c>
       <c r="J41" s="3">
+        <v>198145200</v>
+      </c>
+      <c r="K41" s="3">
         <v>196741400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>192669900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>181637700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>208170000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>212033000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>209767500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>190419900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>165775900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>183905500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>181344200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>132965600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>160626300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>205606000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>189379200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>224065000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>223249900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>534525000</v>
+        <v>563826000</v>
       </c>
       <c r="E42" s="3">
-        <v>525388800</v>
+        <v>547830000</v>
       </c>
       <c r="F42" s="3">
-        <v>550814400</v>
+        <v>538466400</v>
       </c>
       <c r="G42" s="3">
-        <v>516029900</v>
+        <v>564524900</v>
       </c>
       <c r="H42" s="3">
-        <v>511304000</v>
+        <v>528874600</v>
       </c>
       <c r="I42" s="3">
-        <v>543813600</v>
+        <v>524031000</v>
       </c>
       <c r="J42" s="3">
+        <v>557349900</v>
+      </c>
+      <c r="K42" s="3">
         <v>656241000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>579888700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>550086300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>549645200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>534165000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>514620700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>534342900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>545724400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>583172100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>643250700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>720305000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>647419900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>844378300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>764585900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>754124000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>709886700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3797,8 +3889,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3895,8 +3990,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3993,8 +4091,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4091,302 +4192,314 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1109900</v>
+        <v>1160800</v>
       </c>
       <c r="E47" s="3">
-        <v>1094700</v>
+        <v>1137500</v>
       </c>
       <c r="F47" s="3">
-        <v>1082900</v>
+        <v>1122000</v>
       </c>
       <c r="G47" s="3">
-        <v>1105600</v>
+        <v>1109800</v>
       </c>
       <c r="H47" s="3">
-        <v>1160700</v>
+        <v>1133100</v>
       </c>
       <c r="I47" s="3">
-        <v>1214700</v>
+        <v>1189600</v>
       </c>
       <c r="J47" s="3">
+        <v>1244900</v>
+      </c>
+      <c r="K47" s="3">
         <v>1344400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1289400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1159900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1182800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1164100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1174400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1123600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>898700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>955900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1035300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>999300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1084500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1118400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1081100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1101700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1039800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>940400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>934400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>986000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>971600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6758700</v>
+        <v>6888200</v>
       </c>
       <c r="E48" s="3">
-        <v>6684100</v>
+        <v>6926900</v>
       </c>
       <c r="F48" s="3">
-        <v>6626900</v>
+        <v>6850500</v>
       </c>
       <c r="G48" s="3">
-        <v>6495000</v>
+        <v>6791800</v>
       </c>
       <c r="H48" s="3">
-        <v>6593400</v>
+        <v>6656700</v>
       </c>
       <c r="I48" s="3">
-        <v>6595500</v>
+        <v>6757500</v>
       </c>
       <c r="J48" s="3">
+        <v>6759700</v>
+      </c>
+      <c r="K48" s="3">
         <v>6435600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6087900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6035900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6001600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5725900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5689900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5773500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5534600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5979300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5253800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5238500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5755300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6297700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6274900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6506100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2863800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8063100</v>
+        <v>8360200</v>
       </c>
       <c r="E49" s="3">
-        <v>7918300</v>
+        <v>8263800</v>
       </c>
       <c r="F49" s="3">
-        <v>7924800</v>
+        <v>8115400</v>
       </c>
       <c r="G49" s="3">
-        <v>7717300</v>
+        <v>8122000</v>
       </c>
       <c r="H49" s="3">
-        <v>7660000</v>
+        <v>7909400</v>
       </c>
       <c r="I49" s="3">
-        <v>7664300</v>
+        <v>7850700</v>
       </c>
       <c r="J49" s="3">
+        <v>7855100</v>
+      </c>
+      <c r="K49" s="3">
         <v>7996100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7785400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7488700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7397900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7242200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7243100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7249400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6707500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7004800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7527300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7633100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8205700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9371200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9067700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10984700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10812900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,106 +4697,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8410000</v>
+        <v>8784400</v>
       </c>
       <c r="E52" s="3">
-        <v>8400300</v>
+        <v>8619300</v>
       </c>
       <c r="F52" s="3">
-        <v>7541100</v>
+        <v>8609400</v>
       </c>
       <c r="G52" s="3">
-        <v>7461200</v>
+        <v>7728800</v>
       </c>
       <c r="H52" s="3">
-        <v>7438500</v>
+        <v>7646900</v>
       </c>
       <c r="I52" s="3">
-        <v>7858900</v>
+        <v>7623600</v>
       </c>
       <c r="J52" s="3">
+        <v>8054500</v>
+      </c>
+      <c r="K52" s="3">
         <v>6742500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6896400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6949400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6740900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6332200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6231600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6278200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6042200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6341600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6508400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6412400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6988100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7394000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6532500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8867400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11721400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1438179300</v>
+        <v>1496817300</v>
       </c>
       <c r="E54" s="3">
-        <v>1418236100</v>
+        <v>1473977500</v>
       </c>
       <c r="F54" s="3">
-        <v>1467884600</v>
+        <v>1453537800</v>
       </c>
       <c r="G54" s="3">
-        <v>1405226600</v>
+        <v>1504422100</v>
       </c>
       <c r="H54" s="3">
-        <v>1412233900</v>
+        <v>1440204500</v>
       </c>
       <c r="I54" s="3">
-        <v>1444666800</v>
+        <v>1447386200</v>
       </c>
       <c r="J54" s="3">
+        <v>1480626400</v>
+      </c>
+      <c r="K54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,8 +5076,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4967,11 +5097,11 @@
       <c r="H57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I57" s="3">
-        <v>3054100</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3130100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
@@ -4979,24 +5109,24 @@
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>1761700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>1735500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5015,38 +5145,41 @@
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>2940700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5143,106 +5276,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>746800</v>
+        <v>705500</v>
       </c>
       <c r="E59" s="3">
-        <v>681900</v>
+        <v>765400</v>
       </c>
       <c r="F59" s="3">
-        <v>706800</v>
+        <v>698900</v>
       </c>
       <c r="G59" s="3">
-        <v>634400</v>
+        <v>724400</v>
       </c>
       <c r="H59" s="3">
-        <v>553300</v>
+        <v>650200</v>
       </c>
       <c r="I59" s="3">
-        <v>419300</v>
+        <v>567100</v>
       </c>
       <c r="J59" s="3">
+        <v>429700</v>
+      </c>
+      <c r="K59" s="3">
         <v>595500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>750800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>768200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>650500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>855100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>921500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>815700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>572500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>714100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>836700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>711300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>760000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>851400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2138700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1063400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1116700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>985800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5339,204 +5478,213 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>206418000</v>
+        <v>223534700</v>
       </c>
       <c r="E61" s="3">
-        <v>219820900</v>
+        <v>211556000</v>
       </c>
       <c r="F61" s="3">
-        <v>217504900</v>
+        <v>225292500</v>
       </c>
       <c r="G61" s="3">
-        <v>218281900</v>
+        <v>222918900</v>
       </c>
       <c r="H61" s="3">
-        <v>226121300</v>
+        <v>223715300</v>
       </c>
       <c r="I61" s="3">
-        <v>201722400</v>
+        <v>231749800</v>
       </c>
       <c r="J61" s="3">
+        <v>206743500</v>
+      </c>
+      <c r="K61" s="3">
         <v>220125600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>222566500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>210513900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>220593800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>224408700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>214884000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>210056400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>196553600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>216575500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>227441600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>217812200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>220428000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>255682400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>238475100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>267994300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>190280100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3346900</v>
+        <v>4897800</v>
       </c>
       <c r="E62" s="3">
-        <v>3235600</v>
+        <v>3430200</v>
       </c>
       <c r="F62" s="3">
-        <v>3701400</v>
+        <v>3316200</v>
       </c>
       <c r="G62" s="3">
-        <v>3720900</v>
+        <v>3793500</v>
       </c>
       <c r="H62" s="3">
-        <v>3652800</v>
+        <v>3813500</v>
       </c>
       <c r="I62" s="3">
-        <v>3573900</v>
+        <v>3743700</v>
       </c>
       <c r="J62" s="3">
+        <v>3662800</v>
+      </c>
+      <c r="K62" s="3">
         <v>3503600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3722400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4141400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3679400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3266200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3242800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3485100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12807600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3260000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3497500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3710200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3697200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3912600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3751500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4158000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5281600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1358123300</v>
+        <v>1415202700</v>
       </c>
       <c r="E66" s="3">
-        <v>1339285600</v>
+        <v>1391928700</v>
       </c>
       <c r="F66" s="3">
-        <v>1389947700</v>
+        <v>1372622100</v>
       </c>
       <c r="G66" s="3">
-        <v>1328506700</v>
+        <v>1424545300</v>
       </c>
       <c r="H66" s="3">
-        <v>1334875200</v>
+        <v>1361574900</v>
       </c>
       <c r="I66" s="3">
-        <v>1368437500</v>
+        <v>1368102000</v>
       </c>
       <c r="J66" s="3">
+        <v>1402499600</v>
+      </c>
+      <c r="K66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>24641000</v>
+        <v>23578600</v>
       </c>
       <c r="E72" s="3">
-        <v>23036200</v>
+        <v>25254400</v>
       </c>
       <c r="F72" s="3">
-        <v>21799900</v>
+        <v>23609600</v>
       </c>
       <c r="G72" s="3">
-        <v>20587300</v>
+        <v>22342500</v>
       </c>
       <c r="H72" s="3">
-        <v>20842400</v>
+        <v>21099800</v>
       </c>
       <c r="I72" s="3">
-        <v>19236500</v>
+        <v>21361200</v>
       </c>
       <c r="J72" s="3">
+        <v>19715300</v>
+      </c>
+      <c r="K72" s="3">
         <v>17009100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15720900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15034800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13667200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13118800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12484400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11771300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9988000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9959700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10335300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10680000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11258500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14121700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14850900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19841400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19771000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>80056100</v>
+        <v>81614600</v>
       </c>
       <c r="E76" s="3">
-        <v>78950500</v>
+        <v>82048800</v>
       </c>
       <c r="F76" s="3">
-        <v>77936800</v>
+        <v>80915700</v>
       </c>
       <c r="G76" s="3">
-        <v>76720000</v>
+        <v>79876800</v>
       </c>
       <c r="H76" s="3">
-        <v>77358700</v>
+        <v>78629600</v>
       </c>
       <c r="I76" s="3">
-        <v>76229300</v>
+        <v>79284200</v>
       </c>
       <c r="J76" s="3">
+        <v>78126800</v>
+      </c>
+      <c r="K76" s="3">
         <v>74620200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>73028900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>72670000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71910500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>69245700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>67327900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>65506100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>60451400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>62888400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>66729900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>67336400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>70654000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>77200100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>74603800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>80850000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>79454200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1377900</v>
+        <v>-158400</v>
       </c>
       <c r="E81" s="3">
-        <v>1429800</v>
+        <v>1412200</v>
       </c>
       <c r="F81" s="3">
-        <v>1114200</v>
+        <v>1465400</v>
       </c>
       <c r="G81" s="3">
-        <v>825700</v>
+        <v>1141900</v>
       </c>
       <c r="H81" s="3">
-        <v>1251500</v>
+        <v>846200</v>
       </c>
       <c r="I81" s="3">
-        <v>1971200</v>
+        <v>1282600</v>
       </c>
       <c r="J81" s="3">
+        <v>2020300</v>
+      </c>
+      <c r="K81" s="3">
         <v>1205000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1138200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1150100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>225500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>208900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>732100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>960700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>83800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>188900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-84000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-46900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>117200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-502700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>233700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>310700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>47200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>725900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>178400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>670200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,43 +7377,44 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
@@ -7224,8 +7422,8 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -7245,41 +7443,44 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>705000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>692300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>936600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>348100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>732700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>366900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>544200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>814600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,43 +7981,46 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
@@ -7812,8 +8028,8 @@
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -7833,41 +8049,44 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,52 +8121,53 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-240000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-244000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-178000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-154000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-183000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-301000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-249000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-331000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-181000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7967,41 +8187,44 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-153800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AG91" s="3">
         <v>-340400</v>
       </c>
       <c r="AH91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,43 +8422,46 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
@@ -8240,8 +8469,8 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -8261,41 +8490,44 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-923800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>252400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,8 +8562,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8417,19 +8650,22 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,43 +8964,46 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
@@ -8766,8 +9011,8 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -8787,76 +9032,79 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-132500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>911100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
@@ -8864,8 +9112,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8885,76 +9133,79 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1113100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>875000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>430800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>5</v>
@@ -8962,8 +9213,8 @@
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -8983,37 +9234,40 @@
       <c r="W102" s="3">
         <v>0</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,229 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14012200</v>
+        <v>7812800</v>
       </c>
       <c r="E8" s="3">
-        <v>13967900</v>
+        <v>7622400</v>
       </c>
       <c r="F8" s="3">
-        <v>13601300</v>
+        <v>7918900</v>
       </c>
       <c r="G8" s="3">
-        <v>12655400</v>
+        <v>6822200</v>
       </c>
       <c r="H8" s="3">
-        <v>11805900</v>
+        <v>7288300</v>
       </c>
       <c r="I8" s="3">
-        <v>10754800</v>
+        <v>7651700</v>
       </c>
       <c r="J8" s="3">
+        <v>7941100</v>
+      </c>
+      <c r="K8" s="3">
         <v>9102300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6928400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5707100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4801100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4626900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4467000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4179100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4479600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3846000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4143300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4898200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5964000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6438300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7751700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8073600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7778900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -978,31 +984,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>7812800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7622400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7918900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6822200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>7288300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7651700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>7941100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1079,8 +1088,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,28 +1334,31 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-75800</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-47100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>761600</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>146300</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1419,31 +1438,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>338500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>327400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>335500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>490600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>645700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>503600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1520,8 +1542,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11191200</v>
+        <v>5365800</v>
       </c>
       <c r="E17" s="3">
-        <v>10988500</v>
+        <v>7230300</v>
       </c>
       <c r="F17" s="3">
-        <v>10570900</v>
+        <v>5723400</v>
       </c>
       <c r="G17" s="3">
-        <v>9223000</v>
+        <v>5287900</v>
       </c>
       <c r="H17" s="3">
-        <v>8250500</v>
+        <v>5465700</v>
       </c>
       <c r="I17" s="3">
-        <v>7374400</v>
+        <v>5971600</v>
       </c>
       <c r="J17" s="3">
+        <v>5928900</v>
+      </c>
+      <c r="K17" s="3">
         <v>5351900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3346900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2292600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1996400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1733500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1605700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1446300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1589100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1539000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1706300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2354200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2969500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2912700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3733800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3942100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3931900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2821100</v>
+        <v>2447000</v>
       </c>
       <c r="E18" s="3">
-        <v>2979400</v>
+        <v>392200</v>
       </c>
       <c r="F18" s="3">
-        <v>3030400</v>
+        <v>2195500</v>
       </c>
       <c r="G18" s="3">
-        <v>3432500</v>
+        <v>1534200</v>
       </c>
       <c r="H18" s="3">
-        <v>3555400</v>
+        <v>1822600</v>
       </c>
       <c r="I18" s="3">
-        <v>3380400</v>
+        <v>1680100</v>
       </c>
       <c r="J18" s="3">
+        <v>2012200</v>
+      </c>
+      <c r="K18" s="3">
         <v>3750300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3581400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3414500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2804700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2893500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2861300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2732800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2890500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2307000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2437000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2544000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2994500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3525600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4018000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4131500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3847000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,132 +1825,136 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-2365800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-724400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2257300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1524100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1999200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1329100</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>2785500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1112200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2522900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1869700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2313200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2325900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2515800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1965,61 +2001,64 @@
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>326500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>822400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2096,210 +2135,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>455200</v>
+        <v>2522900</v>
       </c>
       <c r="E23" s="3">
-        <v>2255100</v>
+        <v>439300</v>
       </c>
       <c r="F23" s="3">
-        <v>773100</v>
+        <v>2196600</v>
       </c>
       <c r="G23" s="3">
-        <v>1908400</v>
+        <v>772600</v>
       </c>
       <c r="H23" s="3">
-        <v>1556200</v>
+        <v>1822600</v>
       </c>
       <c r="I23" s="3">
-        <v>2051300</v>
+        <v>1533800</v>
       </c>
       <c r="J23" s="3">
+        <v>2012200</v>
+      </c>
+      <c r="K23" s="3">
         <v>857300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1745300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1683300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1798900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>88900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>596600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1232600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1681200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>174500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>500300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>172400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>224700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-841600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>350500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>560400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>780700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>474300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>922300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>396500</v>
+        <v>665800</v>
       </c>
       <c r="E24" s="3">
-        <v>647900</v>
+        <v>383600</v>
       </c>
       <c r="F24" s="3">
-        <v>-809700</v>
+        <v>631100</v>
       </c>
       <c r="G24" s="3">
-        <v>578200</v>
+        <v>-808000</v>
       </c>
       <c r="H24" s="3">
-        <v>516100</v>
+        <v>552500</v>
       </c>
       <c r="I24" s="3">
-        <v>588100</v>
+        <v>508700</v>
       </c>
       <c r="J24" s="3">
+        <v>575800</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>402000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>365600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>467600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-253700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>242300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>357600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>584000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-14000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>179600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>105800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>153800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>223000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>177600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2592800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>108900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>105300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>306800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>340400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>342600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>318600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>400600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>355700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>58700</v>
+        <v>1857000</v>
       </c>
       <c r="E26" s="3">
-        <v>1607100</v>
+        <v>55700</v>
       </c>
       <c r="F26" s="3">
-        <v>1582800</v>
+        <v>1565400</v>
       </c>
       <c r="G26" s="3">
-        <v>1330200</v>
+        <v>1580600</v>
       </c>
       <c r="H26" s="3">
-        <v>1040000</v>
+        <v>1270100</v>
       </c>
       <c r="I26" s="3">
-        <v>1463100</v>
+        <v>1025100</v>
       </c>
       <c r="J26" s="3">
+        <v>1436300</v>
+      </c>
+      <c r="K26" s="3">
         <v>2189700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1343300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1317700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1331300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>342600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>354300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>875000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1097100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>188500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>320700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>66500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>70900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>241600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>253600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>440300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>131800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>728200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>521700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>674900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-158400</v>
+        <v>1821300</v>
       </c>
       <c r="E27" s="3">
-        <v>1412200</v>
+        <v>-606500</v>
       </c>
       <c r="F27" s="3">
-        <v>1465400</v>
+        <v>1534100</v>
       </c>
       <c r="G27" s="3">
-        <v>1141900</v>
+        <v>1546400</v>
       </c>
       <c r="H27" s="3">
-        <v>846200</v>
+        <v>1244700</v>
       </c>
       <c r="I27" s="3">
-        <v>1282600</v>
+        <v>438900</v>
       </c>
       <c r="J27" s="3">
+        <v>1409200</v>
+      </c>
+      <c r="K27" s="3">
         <v>2020300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1205000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1138200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1150100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>225500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>208900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>732100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>960700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>83800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>188900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-84000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-46900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>117200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>233700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>310700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>47200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>725900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>178400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>670200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2767,8 +2827,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2785,12 +2845,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>2365800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>724400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2257300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1524100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1999200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1329100</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>2893100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1836100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1731200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1005800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2804600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2264700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1500200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1209300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2132400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1936700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2371600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2769800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5035000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4859500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5244400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3496500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-158400</v>
+        <v>1821300</v>
       </c>
       <c r="E33" s="3">
-        <v>1412200</v>
+        <v>8600</v>
       </c>
       <c r="F33" s="3">
-        <v>1465400</v>
+        <v>1534100</v>
       </c>
       <c r="G33" s="3">
-        <v>1141900</v>
+        <v>1546400</v>
       </c>
       <c r="H33" s="3">
-        <v>846200</v>
+        <v>1244700</v>
       </c>
       <c r="I33" s="3">
-        <v>1282600</v>
+        <v>982500</v>
       </c>
       <c r="J33" s="3">
+        <v>1409200</v>
+      </c>
+      <c r="K33" s="3">
         <v>2020300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1205000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1138200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1150100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>225500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>208900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>732100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>960700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>83800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>188900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-84000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-46900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>117200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>233700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>310700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>47200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>725900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>178400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>670200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-158400</v>
+        <v>1821300</v>
       </c>
       <c r="E35" s="3">
-        <v>1412200</v>
+        <v>8600</v>
       </c>
       <c r="F35" s="3">
-        <v>1465400</v>
+        <v>1534100</v>
       </c>
       <c r="G35" s="3">
-        <v>1141900</v>
+        <v>1546400</v>
       </c>
       <c r="H35" s="3">
-        <v>846200</v>
+        <v>1244700</v>
       </c>
       <c r="I35" s="3">
-        <v>1282600</v>
+        <v>982500</v>
       </c>
       <c r="J35" s="3">
+        <v>1409200</v>
+      </c>
+      <c r="K35" s="3">
         <v>2020300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1205000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1138200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1150100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>225500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>208900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>732100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>960700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>83800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>188900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-84000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-46900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>117200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>233700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>310700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>47200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>725900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>178400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>670200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,233 +3674,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>164617100</v>
+        <v>157295300</v>
       </c>
       <c r="E41" s="3">
-        <v>164188400</v>
+        <v>144281600</v>
       </c>
       <c r="F41" s="3">
-        <v>197613600</v>
+        <v>159928800</v>
       </c>
       <c r="G41" s="3">
-        <v>187935400</v>
+        <v>181019100</v>
       </c>
       <c r="H41" s="3">
-        <v>182295500</v>
+        <v>179591400</v>
       </c>
       <c r="I41" s="3">
-        <v>178076600</v>
+        <v>163784900</v>
       </c>
       <c r="J41" s="3">
+        <v>174681700</v>
+      </c>
+      <c r="K41" s="3">
         <v>198145200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>196741400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>192669900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>181637700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>208170000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>212033000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>209767500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>190419900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>165775900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>183905500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>181344200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132965600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>160626300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>205606000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>189379200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>224065000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>563826000</v>
+        <v>475900100</v>
       </c>
       <c r="E42" s="3">
-        <v>547830000</v>
+        <v>448251400</v>
       </c>
       <c r="F42" s="3">
-        <v>538466400</v>
+        <v>417080600</v>
       </c>
       <c r="G42" s="3">
-        <v>564524900</v>
+        <v>531073300</v>
       </c>
       <c r="H42" s="3">
-        <v>528874600</v>
+        <v>438541500</v>
       </c>
       <c r="I42" s="3">
-        <v>524031000</v>
+        <v>436538200</v>
       </c>
       <c r="J42" s="3">
+        <v>398974400</v>
+      </c>
+      <c r="K42" s="3">
         <v>557349900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>656241000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>579888700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>550086300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>549645200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>534165000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>514620700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>534342900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>545724400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>583172100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>643250700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>720305000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>647419900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>844378300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>764585900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>754124000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>10383700</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>1676800</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>10500600</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>46065000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>8226100</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>1694300</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>8101900</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3892,31 +3984,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3993,31 +4088,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>40414500</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>14200</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4094,31 +4192,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>643579100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>594209800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>587510000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>798571900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>626368500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>602031700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>581757900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4195,311 +4296,323 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1160800</v>
+        <v>187103500</v>
       </c>
       <c r="E47" s="3">
-        <v>1137500</v>
+        <v>156162000</v>
       </c>
       <c r="F47" s="3">
-        <v>1122000</v>
+        <v>149951500</v>
       </c>
       <c r="G47" s="3">
-        <v>1109800</v>
+        <v>71676800</v>
       </c>
       <c r="H47" s="3">
-        <v>1133100</v>
+        <v>130016900</v>
       </c>
       <c r="I47" s="3">
-        <v>1189600</v>
+        <v>134200900</v>
       </c>
       <c r="J47" s="3">
+        <v>141440700</v>
+      </c>
+      <c r="K47" s="3">
         <v>1244900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1344400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1289400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1159900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1182800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1164100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1174400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1123600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>898700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>955900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1035300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>999300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1084500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1118400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1081100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1101700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>940400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>934400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>986000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>971600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6888200</v>
+        <v>6854800</v>
       </c>
       <c r="E48" s="3">
-        <v>6926900</v>
+        <v>6663500</v>
       </c>
       <c r="F48" s="3">
-        <v>6850500</v>
+        <v>6747200</v>
       </c>
       <c r="G48" s="3">
-        <v>6791800</v>
+        <v>6836500</v>
       </c>
       <c r="H48" s="3">
-        <v>6656700</v>
+        <v>6490300</v>
       </c>
       <c r="I48" s="3">
-        <v>6757500</v>
+        <v>6561100</v>
       </c>
       <c r="J48" s="3">
+        <v>6628600</v>
+      </c>
+      <c r="K48" s="3">
         <v>6759700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6435600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6087900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6035900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6001600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5725900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5689900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5773500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5534600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5979300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5253800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5238500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5755300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6297700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6274900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6506100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8360200</v>
+        <v>8331500</v>
       </c>
       <c r="E49" s="3">
-        <v>8263800</v>
+        <v>8087400</v>
       </c>
       <c r="F49" s="3">
-        <v>8115400</v>
+        <v>8049400</v>
       </c>
       <c r="G49" s="3">
-        <v>8122000</v>
+        <v>8098800</v>
       </c>
       <c r="H49" s="3">
-        <v>7909400</v>
+        <v>7761400</v>
       </c>
       <c r="I49" s="3">
-        <v>7850700</v>
+        <v>7795900</v>
       </c>
       <c r="J49" s="3">
+        <v>7701000</v>
+      </c>
+      <c r="K49" s="3">
         <v>7855100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7996100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7785400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7488700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7397900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7242200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7243100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7249400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6707500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7004800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7527300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7633100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8205700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9371200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9067700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10984700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,109 +4816,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8784400</v>
+        <v>159509300</v>
       </c>
       <c r="E52" s="3">
-        <v>8619300</v>
+        <v>163554100</v>
       </c>
       <c r="F52" s="3">
-        <v>8609400</v>
+        <v>162672300</v>
       </c>
       <c r="G52" s="3">
-        <v>7728800</v>
+        <v>32292500</v>
       </c>
       <c r="H52" s="3">
-        <v>7646900</v>
+        <v>151866000</v>
       </c>
       <c r="I52" s="3">
-        <v>7623600</v>
+        <v>140250000</v>
       </c>
       <c r="J52" s="3">
+        <v>150403100</v>
+      </c>
+      <c r="K52" s="3">
         <v>8054500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6742500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6896400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6949400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6740900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6332200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6231600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6278200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6042200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6341600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6508400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6412400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6988100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7394000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6532500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8867400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1496817300</v>
+        <v>1539250500</v>
       </c>
       <c r="E54" s="3">
-        <v>1473977500</v>
+        <v>1447986700</v>
       </c>
       <c r="F54" s="3">
-        <v>1453537800</v>
+        <v>1435737400</v>
       </c>
       <c r="G54" s="3">
-        <v>1504422100</v>
+        <v>1450570400</v>
       </c>
       <c r="H54" s="3">
-        <v>1440204500</v>
+        <v>1437629100</v>
       </c>
       <c r="I54" s="3">
-        <v>1447386200</v>
+        <v>1419533800</v>
       </c>
       <c r="J54" s="3">
+        <v>1419792500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,59 +5206,60 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>724824900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>686713800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>684731900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>687559400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>647020500</v>
+      </c>
+      <c r="I57" s="3">
+        <v>647623400</v>
       </c>
       <c r="J57" s="3">
+        <v>643130200</v>
+      </c>
+      <c r="K57" s="3">
         <v>3130100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O57" s="3">
         <v>1761700</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>1735500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5148,61 +5278,64 @@
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>267756000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>251066100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>241637700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>393319300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>297073500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>273882100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>257766200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5279,132 +5412,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>705500</v>
+        <v>56543600</v>
       </c>
       <c r="E59" s="3">
-        <v>765400</v>
+        <v>57139200</v>
       </c>
       <c r="F59" s="3">
-        <v>698900</v>
+        <v>52004500</v>
       </c>
       <c r="G59" s="3">
-        <v>724400</v>
+        <v>140061900</v>
       </c>
       <c r="H59" s="3">
-        <v>650200</v>
+        <v>54442200</v>
       </c>
       <c r="I59" s="3">
-        <v>567100</v>
+        <v>63190000</v>
       </c>
       <c r="J59" s="3">
+        <v>66303800</v>
+      </c>
+      <c r="K59" s="3">
         <v>429700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>595500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>750800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>768200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>650500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>855100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>921500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>815700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>572500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>714100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>836700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>711300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>760000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>851400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2138700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1063400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>985800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1049124500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>994919100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>978374200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1226229700</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>998536200</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>984695400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>967200100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5481,210 +5620,219 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>223534700</v>
+        <v>243473100</v>
       </c>
       <c r="E61" s="3">
-        <v>211556000</v>
+        <v>218753900</v>
       </c>
       <c r="F61" s="3">
-        <v>225292500</v>
+        <v>208782000</v>
       </c>
       <c r="G61" s="3">
-        <v>222918900</v>
+        <v>113130300</v>
       </c>
       <c r="H61" s="3">
-        <v>223715300</v>
+        <v>216167400</v>
       </c>
       <c r="I61" s="3">
-        <v>231749800</v>
+        <v>222489100</v>
       </c>
       <c r="J61" s="3">
+        <v>227269700</v>
+      </c>
+      <c r="K61" s="3">
         <v>206743500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>220125600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>222566500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>210513900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>220593800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>224408700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>214884000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>210056400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>196553600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>216575500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>227441600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>217812200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>220428000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>255682400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>238475100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>267994300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4897800</v>
+        <v>160714900</v>
       </c>
       <c r="E62" s="3">
-        <v>3430200</v>
+        <v>153011900</v>
       </c>
       <c r="F62" s="3">
-        <v>3316200</v>
+        <v>166052400</v>
       </c>
       <c r="G62" s="3">
-        <v>3793500</v>
+        <v>27908700</v>
       </c>
       <c r="H62" s="3">
-        <v>3813500</v>
+        <v>143983900</v>
       </c>
       <c r="I62" s="3">
-        <v>3743700</v>
+        <v>132271800</v>
       </c>
       <c r="J62" s="3">
+        <v>144923900</v>
+      </c>
+      <c r="K62" s="3">
         <v>3662800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3503600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3722400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4141400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3679400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3266200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3242800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3485100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12807600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3260000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3497500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3710200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3697200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3912600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3751500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4158000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1415202700</v>
+        <v>1453963900</v>
       </c>
       <c r="E66" s="3">
-        <v>1391928700</v>
+        <v>1367338500</v>
       </c>
       <c r="F66" s="3">
-        <v>1372622100</v>
+        <v>1353861300</v>
       </c>
       <c r="G66" s="3">
-        <v>1424545300</v>
+        <v>1367872200</v>
       </c>
       <c r="H66" s="3">
-        <v>1361574900</v>
+        <v>1359420000</v>
       </c>
       <c r="I66" s="3">
-        <v>1368102000</v>
+        <v>1340151700</v>
       </c>
       <c r="J66" s="3">
+        <v>1340068400</v>
+      </c>
+      <c r="K66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>23578600</v>
+        <v>25510800</v>
       </c>
       <c r="E72" s="3">
-        <v>25254400</v>
+        <v>22809400</v>
       </c>
       <c r="F72" s="3">
-        <v>23609600</v>
+        <v>24599200</v>
       </c>
       <c r="G72" s="3">
-        <v>22342500</v>
+        <v>23561400</v>
       </c>
       <c r="H72" s="3">
-        <v>21099800</v>
+        <v>21350600</v>
       </c>
       <c r="I72" s="3">
-        <v>21361200</v>
+        <v>20796900</v>
       </c>
       <c r="J72" s="3">
+        <v>20953900</v>
+      </c>
+      <c r="K72" s="3">
         <v>19715300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17009100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15720900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15034800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13667200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13118800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12484400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11771300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9988000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9959700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10335300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10680000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11258500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14121700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14850900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19841400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>81614600</v>
+        <v>83553400</v>
       </c>
       <c r="E76" s="3">
-        <v>82048800</v>
+        <v>78952100</v>
       </c>
       <c r="F76" s="3">
-        <v>80915700</v>
+        <v>79919100</v>
       </c>
       <c r="G76" s="3">
-        <v>79876800</v>
+        <v>80749400</v>
       </c>
       <c r="H76" s="3">
-        <v>78629600</v>
+        <v>76331500</v>
       </c>
       <c r="I76" s="3">
-        <v>79284200</v>
+        <v>77501100</v>
       </c>
       <c r="J76" s="3">
+        <v>77770500</v>
+      </c>
+      <c r="K76" s="3">
         <v>78126800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74620200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>73028900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>72670000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71910500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>69245700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>67327900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>65506100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60451400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>62888400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>66729900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>67336400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>70654000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>77200100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>74603800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>80850000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-158400</v>
+        <v>1821300</v>
       </c>
       <c r="E81" s="3">
-        <v>1412200</v>
+        <v>8600</v>
       </c>
       <c r="F81" s="3">
-        <v>1465400</v>
+        <v>1534100</v>
       </c>
       <c r="G81" s="3">
-        <v>1141900</v>
+        <v>1546400</v>
       </c>
       <c r="H81" s="3">
-        <v>846200</v>
+        <v>1244700</v>
       </c>
       <c r="I81" s="3">
-        <v>1282600</v>
+        <v>982500</v>
       </c>
       <c r="J81" s="3">
+        <v>1409200</v>
+      </c>
+      <c r="K81" s="3">
         <v>2020300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1205000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1138200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1150100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>225500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>208900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>732100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>960700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>83800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>188900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-84000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-46900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>117200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>233700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>310700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>47200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>725900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>178400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>670200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,46 +7575,47 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
@@ -7425,8 +7623,8 @@
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -7446,41 +7644,44 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>705000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>692300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>936600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>348100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>732700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>366900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>544200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>814600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,46 +8197,49 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
@@ -8031,8 +8247,8 @@
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -8052,41 +8268,44 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-240000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-244000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-178000</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-249000</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-331000</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-181000</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-153800</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-154000</v>
       </c>
-      <c r="H91" s="3">
-        <v>-183000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-301000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-249000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-331000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-181000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-153800</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-154000</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AH91" s="3">
         <v>-340400</v>
       </c>
       <c r="AI91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,46 +8651,49 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
@@ -8472,8 +8701,8 @@
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8493,41 +8722,44 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>252400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,31 +8795,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8653,19 +8886,22 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,46 +9209,49 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
@@ -9014,8 +9259,8 @@
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -9035,79 +9280,82 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>911100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
@@ -9115,8 +9363,8 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -9136,79 +9384,82 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>875000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>430800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>5</v>
@@ -9216,8 +9467,8 @@
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
@@ -9237,37 +9488,40 @@
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,235 +656,241 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8506100</v>
+      </c>
+      <c r="E8" s="3">
         <v>7812800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7622400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7918900</v>
       </c>
-      <c r="G8" s="3">
-        <v>6822200</v>
-      </c>
       <c r="H8" s="3">
+        <v>9336800</v>
+      </c>
+      <c r="I8" s="3">
         <v>7288300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7651700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7941100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9102300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6928400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5707100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4801100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4626900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4467000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4179100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4479600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3846000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4143300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4898200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5964000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6438300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7751700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8073600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7778900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -987,35 +993,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8506100</v>
+      </c>
+      <c r="E10" s="3">
         <v>7812800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7622400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7918900</v>
       </c>
-      <c r="G10" s="3">
-        <v>6822200</v>
-      </c>
       <c r="H10" s="3">
+        <v>9336800</v>
+      </c>
+      <c r="I10" s="3">
         <v>7288300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7651700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7941100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1091,8 +1100,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,32 +1353,35 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2281800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-75800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-47100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>761600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>146300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1441,35 +1460,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>245900</v>
+      </c>
+      <c r="E15" s="3">
         <v>338500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>720000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>327400</v>
       </c>
-      <c r="G15" s="3">
-        <v>335500</v>
-      </c>
       <c r="H15" s="3">
+        <v>470900</v>
+      </c>
+      <c r="I15" s="3">
         <v>490600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>645700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>503600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1545,8 +1567,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4157800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5365800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7230300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5723400</v>
       </c>
-      <c r="G17" s="3">
-        <v>5287900</v>
-      </c>
       <c r="H17" s="3">
+        <v>5286800</v>
+      </c>
+      <c r="I17" s="3">
         <v>5465700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5971600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5928900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5351900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3346900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2292600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1996400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1733500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1605700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1446300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1589100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1539000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1706300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2354200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2969500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2912700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3733800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3942100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3931900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4348300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2447000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>392200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2195500</v>
       </c>
-      <c r="G18" s="3">
-        <v>1534200</v>
-      </c>
       <c r="H18" s="3">
+        <v>4050000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1822600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1680100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2012200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3750300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3581400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3414500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2804700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2893500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2861300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2732800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2890500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2307000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2437000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2544000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2994500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3525600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4018000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4131500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3847000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1852,113 +1885,116 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4594200</v>
+      </c>
+      <c r="E21" s="3">
         <v>2785500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1112200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2522900</v>
       </c>
-      <c r="G21" s="3">
-        <v>1869700</v>
-      </c>
       <c r="H21" s="3">
+        <v>4520800</v>
+      </c>
+      <c r="I21" s="3">
         <v>2313200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2325900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2515800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2004,38 +2040,41 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>326500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>822400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,8 +2099,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2138,216 +2177,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2066500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2522900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>439300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2196600</v>
       </c>
-      <c r="G23" s="3">
-        <v>772600</v>
-      </c>
       <c r="H23" s="3">
+        <v>3288400</v>
+      </c>
+      <c r="I23" s="3">
         <v>1822600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1533800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2012200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>857300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1745300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1683300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1798900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>88900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>596600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1232600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1681200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>174500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>500300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>172400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>224700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-841600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>350500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>560400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>780700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>474300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>922300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>707100</v>
+      </c>
+      <c r="E24" s="3">
         <v>665800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>383600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>631100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-808000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="I24" s="3">
         <v>552500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>508700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>575800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>402000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>365600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>467600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-253700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>242300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>357600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>584000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-14000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>179600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>105800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>153800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>223000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>177600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2592800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>108900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>105300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>306800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>340400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>342600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>318600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>400600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>355700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1359400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1857000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>55700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1565400</v>
       </c>
-      <c r="G26" s="3">
-        <v>1580600</v>
-      </c>
       <c r="H26" s="3">
+        <v>3305000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1270100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1025100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1436300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2189700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1343300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1317700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1331300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>342600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>354300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>875000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1097100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>188500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>320700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>66500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>70900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>241600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>253600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>440300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>131800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>728200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>521700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>674900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1821300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-606500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1534100</v>
       </c>
-      <c r="G27" s="3">
-        <v>1546400</v>
-      </c>
       <c r="H27" s="3">
+        <v>3270700</v>
+      </c>
+      <c r="I27" s="3">
         <v>1244700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>438900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1409200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2020300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1205000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1138200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1150100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>225500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>208900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>732100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>960700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>83800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>188900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-84000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-46900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>117200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>233700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>310700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>47200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>725900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>178400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>670200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,8 +2890,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2848,12 +2908,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3100,190 +3169,196 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>2893100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1836100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1731200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1005800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2804600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2264700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1500200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1209300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2132400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1936700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2371600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2769800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5035000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4859500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5244400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3496500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1821300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1534100</v>
       </c>
-      <c r="G33" s="3">
-        <v>1546400</v>
-      </c>
       <c r="H33" s="3">
+        <v>3270700</v>
+      </c>
+      <c r="I33" s="3">
         <v>1244700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>982500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1409200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2020300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1205000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1138200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1150100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>225500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>208900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>732100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>960700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>83800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>188900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-84000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-46900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>117200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>233700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>310700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>47200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>725900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>178400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>670200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1821300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1534100</v>
       </c>
-      <c r="G35" s="3">
-        <v>1546400</v>
-      </c>
       <c r="H35" s="3">
+        <v>3270700</v>
+      </c>
+      <c r="I35" s="3">
         <v>1244700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>982500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1409200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2020300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1205000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1138200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1150100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>225500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>208900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>732100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>960700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>83800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>188900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-84000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-46900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>117200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>233700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>310700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>47200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>725900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>178400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>670200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,243 +3760,250 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>135279000</v>
+      </c>
+      <c r="E41" s="3">
         <v>157295300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>144281600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>159928800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>181019100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>179591400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>163784900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>174681700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>198145200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>196741400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>192669900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>181637700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>208170000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>212033000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>209767500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>190419900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>165775900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>183905500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>181344200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>132965600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>160626300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>205606000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>189379200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>224065000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>607604300</v>
+      </c>
+      <c r="E42" s="3">
         <v>475900100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>448251400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>417080600</v>
       </c>
-      <c r="G42" s="3">
-        <v>531073300</v>
-      </c>
       <c r="H42" s="3">
+        <v>531096500</v>
+      </c>
+      <c r="I42" s="3">
         <v>438541500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>436538200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>398974400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>557349900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>656241000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>579888700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>550086300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>549645200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>534165000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>514620700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>534342900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>545724400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>583172100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>643250700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>720305000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>647419900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>844378300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>764585900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>754124000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>45537800</v>
+      </c>
+      <c r="E43" s="3">
         <v>10383700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1676800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10500600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46065000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8226100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1694300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8101900</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3987,8 +4079,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4013,8 +4108,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4091,13 +4186,16 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>23927900</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
@@ -4105,20 +4203,20 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
-        <v>40414500</v>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
+        <v>40413400</v>
+      </c>
+      <c r="I45" s="3">
         <v>9500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4195,35 +4293,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>812349100</v>
+      </c>
+      <c r="E46" s="3">
         <v>643579100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>594209800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>587510000</v>
       </c>
-      <c r="G46" s="3">
-        <v>798571900</v>
-      </c>
       <c r="H46" s="3">
+        <v>798594000</v>
+      </c>
+      <c r="I46" s="3">
         <v>626368500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>602031700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>581757900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4299,320 +4400,332 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>72156500</v>
+      </c>
+      <c r="E47" s="3">
         <v>187103500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>156162000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>149951500</v>
       </c>
-      <c r="G47" s="3">
-        <v>71676800</v>
-      </c>
       <c r="H47" s="3">
+        <v>71701100</v>
+      </c>
+      <c r="I47" s="3">
         <v>130016900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>134200900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>141440700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1244900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1344400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1289400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1159900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1182800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1164100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1174400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1123600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>898700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>955900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1035300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>999300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1084500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1118400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1081100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1101700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>940400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>934400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>986000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>971600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6411600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6854800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6663500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6747200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6836500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6490300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6561100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6628600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6759700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6435600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6087900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6035900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6001600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5725900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5689900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5773500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5534600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5979300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5253800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5238500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5755300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6297700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6274900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6506100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8022600</v>
+      </c>
+      <c r="E49" s="3">
         <v>8331500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8087400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8049400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8098800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7761400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7795900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7701000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7855100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7996100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7785400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7488700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7397900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7242200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7243100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7249400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6707500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7004800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7527300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7633100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8205700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9371200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9067700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10984700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,112 +4935,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>31260000</v>
+      </c>
+      <c r="E52" s="3">
         <v>159509300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>163554100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>162672300</v>
       </c>
-      <c r="G52" s="3">
-        <v>32292500</v>
-      </c>
       <c r="H52" s="3">
+        <v>32269300</v>
+      </c>
+      <c r="I52" s="3">
         <v>151866000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>140250000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>150403100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8054500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6742500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6896400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6949400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6740900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6332200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6231600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6278200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6042200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6341600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6508400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6412400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6988100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7394000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6532500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8867400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1440141800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1539250500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1447986700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1435737400</v>
       </c>
-      <c r="G54" s="3">
-        <v>1450570400</v>
-      </c>
       <c r="H54" s="3">
+        <v>1456025200</v>
+      </c>
+      <c r="I54" s="3">
         <v>1437629100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1419533800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1419792500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,62 +5336,63 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>691272400</v>
+      </c>
+      <c r="E57" s="3">
         <v>724824900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>686713800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>684731900</v>
       </c>
-      <c r="G57" s="3">
-        <v>687559400</v>
-      </c>
       <c r="H57" s="3">
+        <v>691373900</v>
+      </c>
+      <c r="I57" s="3">
         <v>647020500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>647623400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>643130200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3130100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>1761700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>1735500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5281,65 +5411,68 @@
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>396425100</v>
+      </c>
+      <c r="E58" s="3">
         <v>267756000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>251066100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>241637700</v>
       </c>
-      <c r="G58" s="3">
-        <v>393319300</v>
-      </c>
       <c r="H58" s="3">
+        <v>393339200</v>
+      </c>
+      <c r="I58" s="3">
         <v>297073500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>273882100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>257766200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5415,139 +5548,145 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>114859700</v>
+      </c>
+      <c r="E59" s="3">
         <v>56543600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57139200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52004500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>140061900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>54442200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>63190000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>66303800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>429700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>595500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>750800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>768200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>650500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>855100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>921500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>815700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>572500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>714100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>836700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>711300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>760000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>851400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2138700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1063400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>985800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1207850700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1049124500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>994919100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>978374200</v>
       </c>
-      <c r="G60" s="3">
-        <v>1226229700</v>
-      </c>
       <c r="H60" s="3">
+        <v>1230064100</v>
+      </c>
+      <c r="I60" s="3">
         <v>998536200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>984695400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>967200100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5623,216 +5762,225 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>122324300</v>
+      </c>
+      <c r="E61" s="3">
         <v>243473100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>218753900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>208782000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>113130300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>216167400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>222489100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>227269700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>206743500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>220125600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>222566500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>210513900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>220593800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>224408700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>214884000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>210056400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>196553600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>216575500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>227441600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>217812200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>220428000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>255682400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>238475100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>267994300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24617500</v>
+      </c>
+      <c r="E62" s="3">
         <v>160714900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>153011900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>166052400</v>
       </c>
-      <c r="G62" s="3">
-        <v>27908700</v>
-      </c>
       <c r="H62" s="3">
+        <v>27887700</v>
+      </c>
+      <c r="I62" s="3">
         <v>143983900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>132271800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>144923900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3662800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3503600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3722400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4141400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3679400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3266200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3242800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3485100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12807600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3260000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3497500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3710200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3697200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3912600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3751500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4158000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1355386700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1453963900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1367338500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1353861300</v>
       </c>
-      <c r="G66" s="3">
-        <v>1367872200</v>
-      </c>
       <c r="H66" s="3">
+        <v>1371653600</v>
+      </c>
+      <c r="I66" s="3">
         <v>1359420000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1340151700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1340068400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26785400</v>
+      </c>
+      <c r="E72" s="3">
         <v>25510800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22809400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24599200</v>
       </c>
-      <c r="G72" s="3">
-        <v>23561400</v>
-      </c>
       <c r="H72" s="3">
+        <v>25251500</v>
+      </c>
+      <c r="I72" s="3">
         <v>21350600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20796900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20953900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19715300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17009100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15720900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15034800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13667200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13118800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12484400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11771300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9988000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9959700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10335300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10680000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11258500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14121700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14850900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19841400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>83092500</v>
+      </c>
+      <c r="E76" s="3">
         <v>83553400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>78952100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79919100</v>
       </c>
-      <c r="G76" s="3">
-        <v>80749400</v>
-      </c>
       <c r="H76" s="3">
+        <v>82422900</v>
+      </c>
+      <c r="I76" s="3">
         <v>76331500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>77501100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>77770500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>78126800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>74620200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>73028900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>72670000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71910500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>69245700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>67327900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>65506100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>60451400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>62888400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>66729900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>67336400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>70654000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>77200100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>74603800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>80850000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1821300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1534100</v>
       </c>
-      <c r="G81" s="3">
-        <v>1546400</v>
-      </c>
       <c r="H81" s="3">
+        <v>3270700</v>
+      </c>
+      <c r="I81" s="3">
         <v>1244700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>982500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1409200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2020300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1205000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1138200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1150100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>225500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>208900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>732100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>960700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>83800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>188900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-84000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-46900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>117200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>233700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>310700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>47200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>725900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>178400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>670200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,8 +7773,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7602,23 +7800,23 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
@@ -7626,8 +7824,8 @@
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -7647,41 +7845,44 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>705000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>692300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>936600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>348100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>732700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>366900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>544200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>814600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,8 +8413,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8226,23 +8442,23 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
@@ -8250,8 +8466,8 @@
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
@@ -8271,41 +8487,44 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,8 +8561,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8368,32 +8588,32 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-249000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-331000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-181000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8413,41 +8633,44 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AI91" s="3">
         <v>-340400</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,8 +8880,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8680,23 +8909,23 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
@@ -8704,8 +8933,8 @@
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8725,41 +8954,44 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>252400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,8 +9028,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8822,8 +9055,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8889,19 +9122,22 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,8 +9454,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9238,23 +9483,23 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
@@ -9262,8 +9507,8 @@
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -9283,41 +9528,44 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>911100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,23 +9590,23 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
@@ -9366,8 +9614,8 @@
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -9387,41 +9635,44 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>875000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>430800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9446,23 +9697,23 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
@@ -9470,8 +9721,8 @@
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -9491,37 +9742,40 @@
       <c r="Y102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,241 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8506100</v>
+        <v>8705100</v>
       </c>
       <c r="E8" s="3">
+        <v>7044200</v>
+      </c>
+      <c r="F8" s="3">
         <v>7812800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7622400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7918900</v>
       </c>
-      <c r="H8" s="3">
-        <v>9336800</v>
-      </c>
       <c r="I8" s="3">
+        <v>6822200</v>
+      </c>
+      <c r="J8" s="3">
         <v>7288300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7651700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7941100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9102300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6928400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5707100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4801100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4626900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4467000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4179100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4479600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3846000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4143300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4898200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5964000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6438300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7751700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8073600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7778900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -996,38 +1002,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8506100</v>
+        <v>8705100</v>
       </c>
       <c r="E10" s="3">
+        <v>7044200</v>
+      </c>
+      <c r="F10" s="3">
         <v>7812800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7622400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7918900</v>
       </c>
-      <c r="H10" s="3">
-        <v>9336800</v>
-      </c>
       <c r="I10" s="3">
+        <v>6822200</v>
+      </c>
+      <c r="J10" s="3">
         <v>7288300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7651700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7941100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,35 +1372,38 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2281800</v>
+        <v>-5400</v>
       </c>
       <c r="E14" s="3">
+        <v>2220700</v>
+      </c>
+      <c r="F14" s="3">
         <v>-75800</v>
       </c>
-      <c r="F14" s="3">
-        <v>-47100</v>
-      </c>
       <c r="G14" s="3">
-        <v>-1100</v>
+        <v>-49300</v>
       </c>
       <c r="H14" s="3">
-        <v>761600</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>696400</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>146300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1463,38 +1482,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>245900</v>
+        <v>426900</v>
       </c>
       <c r="E15" s="3">
+        <v>408900</v>
+      </c>
+      <c r="F15" s="3">
         <v>338500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>720000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>327400</v>
       </c>
-      <c r="H15" s="3">
-        <v>470900</v>
-      </c>
       <c r="I15" s="3">
+        <v>335500</v>
+      </c>
+      <c r="J15" s="3">
         <v>490600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>645700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>503600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1592,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4157800</v>
+        <v>5644200</v>
       </c>
       <c r="E17" s="3">
+        <v>4219900</v>
+      </c>
+      <c r="F17" s="3">
         <v>5365800</v>
       </c>
-      <c r="F17" s="3">
-        <v>7230300</v>
-      </c>
       <c r="G17" s="3">
-        <v>5723400</v>
+        <v>7232400</v>
       </c>
       <c r="H17" s="3">
-        <v>5286800</v>
+        <v>5721200</v>
       </c>
       <c r="I17" s="3">
+        <v>5353200</v>
+      </c>
+      <c r="J17" s="3">
         <v>5465700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5971600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5928900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5351900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3346900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2292600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1996400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1733500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1605700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1446300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1589100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1539000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1706300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2354200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2969500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2912700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3733800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3942100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3931900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4348300</v>
+        <v>3061000</v>
       </c>
       <c r="E18" s="3">
+        <v>2824300</v>
+      </c>
+      <c r="F18" s="3">
         <v>2447000</v>
       </c>
-      <c r="F18" s="3">
-        <v>392200</v>
-      </c>
       <c r="G18" s="3">
-        <v>2195500</v>
+        <v>390000</v>
       </c>
       <c r="H18" s="3">
-        <v>4050000</v>
+        <v>2197600</v>
       </c>
       <c r="I18" s="3">
+        <v>1469000</v>
+      </c>
+      <c r="J18" s="3">
         <v>1822600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1680100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2012200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3750300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3581400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3414500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2804700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2893500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2861300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2732800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2890500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2307000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2437000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2544000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2994500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3525600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4018000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4131500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3847000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,8 +1891,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1888,116 +1921,119 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4594200</v>
+        <v>3487900</v>
       </c>
       <c r="E21" s="3">
+        <v>3233300</v>
+      </c>
+      <c r="F21" s="3">
         <v>2785500</v>
       </c>
-      <c r="F21" s="3">
-        <v>1112200</v>
-      </c>
       <c r="G21" s="3">
-        <v>2522900</v>
+        <v>1110000</v>
       </c>
       <c r="H21" s="3">
-        <v>4520800</v>
+        <v>2525100</v>
       </c>
       <c r="I21" s="3">
+        <v>1804500</v>
+      </c>
+      <c r="J21" s="3">
         <v>2313200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2325900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2515800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2043,38 +2079,41 @@
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>326500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>822400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,8 +2141,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2180,222 +2219,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2066500</v>
+        <v>3066400</v>
       </c>
       <c r="E23" s="3">
+        <v>603600</v>
+      </c>
+      <c r="F23" s="3">
         <v>2522900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>439300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2196600</v>
       </c>
-      <c r="H23" s="3">
-        <v>3288400</v>
-      </c>
       <c r="I23" s="3">
+        <v>772600</v>
+      </c>
+      <c r="J23" s="3">
         <v>1822600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1533800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2012200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>857300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1745300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1683300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1798900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>88900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>596600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1232600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1681200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>174500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>500300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>172400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>224700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-841600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>350500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>560400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>780700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>474300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>922300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>707100</v>
+        <v>891700</v>
       </c>
       <c r="E24" s="3">
+        <v>254700</v>
+      </c>
+      <c r="F24" s="3">
         <v>665800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>383600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>631100</v>
       </c>
-      <c r="H24" s="3">
-        <v>-16600</v>
-      </c>
       <c r="I24" s="3">
+        <v>-808000</v>
+      </c>
+      <c r="J24" s="3">
         <v>552500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>508700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>575800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>402000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>365600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>467600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-253700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>242300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>357600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>584000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-14000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>179600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>105800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>153800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>223000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>177600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2592800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>108900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>105300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>306800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>340400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>342600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>318600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>400600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>355700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1359400</v>
+        <v>2174700</v>
       </c>
       <c r="E26" s="3">
+        <v>348900</v>
+      </c>
+      <c r="F26" s="3">
         <v>1857000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>55700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1565400</v>
       </c>
-      <c r="H26" s="3">
-        <v>3305000</v>
-      </c>
       <c r="I26" s="3">
+        <v>1580600</v>
+      </c>
+      <c r="J26" s="3">
         <v>1270100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1025100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1436300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2189700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1343300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1317700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1331300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>342600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>354300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>875000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1097100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>188500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>320700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>66500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>70900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>241600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>253600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>440300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>131800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>728200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>521700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>674900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1324200</v>
+        <v>2127100</v>
       </c>
       <c r="E27" s="3">
+        <v>313700</v>
+      </c>
+      <c r="F27" s="3">
         <v>1821300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-606500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1534100</v>
       </c>
-      <c r="H27" s="3">
-        <v>3270700</v>
-      </c>
       <c r="I27" s="3">
+        <v>1546400</v>
+      </c>
+      <c r="J27" s="3">
         <v>1244700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>438900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1409200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2020300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1205000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1138200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1150100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>225500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>208900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>732100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>960700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>83800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>188900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-84000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-46900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>117200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>233700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>310700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>47200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>725900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>178400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>670200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2953,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2911,12 +2971,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3172,193 +3241,199 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>2893100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1836100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1731200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1005800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2804600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2264700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1209300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2132400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1936700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2371600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2769800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5035000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4859500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5244400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3496500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1324200</v>
+        <v>2127100</v>
       </c>
       <c r="E33" s="3">
+        <v>313700</v>
+      </c>
+      <c r="F33" s="3">
         <v>1821300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1534100</v>
       </c>
-      <c r="H33" s="3">
-        <v>3270700</v>
-      </c>
       <c r="I33" s="3">
+        <v>1546400</v>
+      </c>
+      <c r="J33" s="3">
         <v>1244700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>982500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1409200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2020300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1205000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1138200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1150100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>225500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>208900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>732100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>960700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>83800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>188900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-84000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-46900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>117200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>233700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>310700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>47200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>725900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>178400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>670200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1324200</v>
+        <v>2127100</v>
       </c>
       <c r="E35" s="3">
+        <v>313700</v>
+      </c>
+      <c r="F35" s="3">
         <v>1821300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1534100</v>
       </c>
-      <c r="H35" s="3">
-        <v>3270700</v>
-      </c>
       <c r="I35" s="3">
+        <v>1546400</v>
+      </c>
+      <c r="J35" s="3">
         <v>1244700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>982500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1409200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2020300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1205000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1138200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1150100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>225500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>208900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>732100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>960700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>83800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>188900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-84000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-46900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>117200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>233700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>310700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>47200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>725900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>178400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>670200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,252 +3846,259 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>163802400</v>
+      </c>
+      <c r="E41" s="3">
         <v>135279000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>157295300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>144281600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>159928800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>181019100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>179591400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>163784900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>174681700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>198145200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>196741400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>192669900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>181637700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>208170000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>212033000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>209767500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>190419900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>165775900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>183905500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>181344200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>132965600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>160626300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>205606000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>189379200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>224065000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>607604300</v>
+        <v>465543700</v>
       </c>
       <c r="E42" s="3">
+        <v>607556700</v>
+      </c>
+      <c r="F42" s="3">
         <v>475900100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>448251400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>417080600</v>
       </c>
-      <c r="H42" s="3">
-        <v>531096500</v>
-      </c>
       <c r="I42" s="3">
+        <v>531073300</v>
+      </c>
+      <c r="J42" s="3">
         <v>438541500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>436538200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>398974400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>557349900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>656241000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>579888700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>550086300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>549645200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>534165000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>514620700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>534342900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>545724400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>583172100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>643250700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>720305000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>647419900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>844378300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>764585900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>754124000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9971900</v>
+      </c>
+      <c r="E43" s="3">
         <v>45537800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10383700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1676800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10500600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46065000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8226100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1694300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8101900</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4082,8 +4174,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4111,8 +4206,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4189,37 +4284,40 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>23927900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>40413400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4296,38 +4394,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>812349100</v>
+        <v>639318000</v>
       </c>
       <c r="E46" s="3">
+        <v>812301500</v>
+      </c>
+      <c r="F46" s="3">
         <v>643579100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>594209800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>587510000</v>
       </c>
-      <c r="H46" s="3">
-        <v>798594000</v>
-      </c>
       <c r="I46" s="3">
+        <v>798570800</v>
+      </c>
+      <c r="J46" s="3">
         <v>626368500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>602031700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>581757900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4403,329 +4504,341 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>72156500</v>
+        <v>167032000</v>
       </c>
       <c r="E47" s="3">
+        <v>72140000</v>
+      </c>
+      <c r="F47" s="3">
         <v>187103500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>156162000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>149951500</v>
       </c>
-      <c r="H47" s="3">
-        <v>71701100</v>
-      </c>
       <c r="I47" s="3">
+        <v>71676800</v>
+      </c>
+      <c r="J47" s="3">
         <v>130016900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>134200900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>141440700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1244900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1344400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1289400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1159900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1182800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1164100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1174400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1123600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>898700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>955900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1035300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>999300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1084500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1118400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1081100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1101700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>940400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>934400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>986000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>971600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6665600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6411600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6854800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6663500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6747200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6836500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6490300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6561100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6628600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6759700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6435600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6087900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6035900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6001600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5725900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5689900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5773500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5534600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5979300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5253800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5238500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5755300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6297700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6274900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6506100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8243600</v>
+      </c>
+      <c r="E49" s="3">
         <v>8022600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8331500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8087400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8049400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8098800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7761400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7795900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7701000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7855100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7996100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7785400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7488700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7397900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7242200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7243100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7249400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6707500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7004800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7527300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7633100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8205700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9371200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9067700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10984700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,115 +5054,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>31260000</v>
+        <v>187452400</v>
       </c>
       <c r="E52" s="3">
+        <v>31306600</v>
+      </c>
+      <c r="F52" s="3">
         <v>159509300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>163554100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>162672300</v>
       </c>
-      <c r="H52" s="3">
-        <v>32269300</v>
-      </c>
       <c r="I52" s="3">
+        <v>32293600</v>
+      </c>
+      <c r="J52" s="3">
         <v>151866000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>140250000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>150403100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8054500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6742500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6896400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6949400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6740900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6332200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6231600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6278200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6042200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6341600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6508400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6412400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6988100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7394000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6532500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8867400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1440141800</v>
+        <v>1531395400</v>
       </c>
       <c r="E54" s="3">
+        <v>1436149700</v>
+      </c>
+      <c r="F54" s="3">
         <v>1539250500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1447986700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1435737400</v>
       </c>
-      <c r="H54" s="3">
-        <v>1456025200</v>
-      </c>
       <c r="I54" s="3">
+        <v>1450570400</v>
+      </c>
+      <c r="J54" s="3">
         <v>1437629100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1419533800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1419792500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,65 +5466,66 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>691272400</v>
+        <v>718679200</v>
       </c>
       <c r="E57" s="3">
+        <v>689782600</v>
+      </c>
+      <c r="F57" s="3">
         <v>724824900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>686713800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>684731900</v>
       </c>
-      <c r="H57" s="3">
-        <v>691373900</v>
-      </c>
       <c r="I57" s="3">
+        <v>687559400</v>
+      </c>
+      <c r="J57" s="3">
         <v>647020500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>647623400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>643130200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3130100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1761700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>1735500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5414,68 +5544,71 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>396425100</v>
+        <v>252522700</v>
       </c>
       <c r="E58" s="3">
+        <v>396409600</v>
+      </c>
+      <c r="F58" s="3">
         <v>267756000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>251066100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>241637700</v>
       </c>
-      <c r="H58" s="3">
-        <v>393339200</v>
-      </c>
       <c r="I58" s="3">
+        <v>393319300</v>
+      </c>
+      <c r="J58" s="3">
         <v>297073500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>273882100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>257766200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5551,145 +5684,151 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>114859700</v>
+        <v>55089700</v>
       </c>
       <c r="E59" s="3">
+        <v>114861800</v>
+      </c>
+      <c r="F59" s="3">
         <v>56543600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57139200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52004500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>140061900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>54442200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>63190000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>66303800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>429700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>595500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>750800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>768200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>650500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>855100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>921500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>815700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>572500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>714100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>836700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>711300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>760000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>851400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2138700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1063400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>985800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1207850700</v>
+        <v>1026291600</v>
       </c>
       <c r="E60" s="3">
+        <v>1206347400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1049124500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>994919100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>978374200</v>
       </c>
-      <c r="H60" s="3">
-        <v>1230064100</v>
-      </c>
       <c r="I60" s="3">
+        <v>1226229700</v>
+      </c>
+      <c r="J60" s="3">
         <v>998536200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>984695400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>967200100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5765,222 +5904,231 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>122324300</v>
+        <v>241588800</v>
       </c>
       <c r="E61" s="3">
+        <v>122314900</v>
+      </c>
+      <c r="F61" s="3">
         <v>243473100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>218753900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>208782000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>113130300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>216167400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>222489100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>227269700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>206743500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>220125600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>222566500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>210513900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>220593800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>224408700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>214884000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>210056400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>196553600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>216575500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>227441600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>217812200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>220428000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>255682400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>238475100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>267994300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24617500</v>
+        <v>174706000</v>
       </c>
       <c r="E62" s="3">
+        <v>24640200</v>
+      </c>
+      <c r="F62" s="3">
         <v>160714900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>153011900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>166052400</v>
       </c>
-      <c r="H62" s="3">
-        <v>27887700</v>
-      </c>
       <c r="I62" s="3">
+        <v>27908700</v>
+      </c>
+      <c r="J62" s="3">
         <v>143983900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>132271800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>144923900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3662800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3503600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3722400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4141400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3679400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3266200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3242800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3485100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12807600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3260000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3497500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3710200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3697200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3912600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3751500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4158000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1355386700</v>
+        <v>1443233900</v>
       </c>
       <c r="E66" s="3">
+        <v>1353913400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1453963900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1367338500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1353861300</v>
       </c>
-      <c r="H66" s="3">
-        <v>1371653600</v>
-      </c>
       <c r="I66" s="3">
+        <v>1367872200</v>
+      </c>
+      <c r="J66" s="3">
         <v>1359420000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1340151700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1340068400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>26785400</v>
+        <v>27329200</v>
       </c>
       <c r="E72" s="3">
+        <v>24193000</v>
+      </c>
+      <c r="F72" s="3">
         <v>25510800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22809400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24599200</v>
       </c>
-      <c r="H72" s="3">
-        <v>25251500</v>
-      </c>
       <c r="I72" s="3">
+        <v>23561400</v>
+      </c>
+      <c r="J72" s="3">
         <v>21350600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20796900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20953900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19715300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17009100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15720900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15034800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13667200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13118800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12484400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11771300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9988000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9959700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10335300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10680000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11258500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14121700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14850900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19841400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>83092500</v>
+        <v>86467800</v>
       </c>
       <c r="E76" s="3">
+        <v>80573600</v>
+      </c>
+      <c r="F76" s="3">
         <v>83553400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>78952100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>79919100</v>
       </c>
-      <c r="H76" s="3">
-        <v>82422900</v>
-      </c>
       <c r="I76" s="3">
+        <v>80749400</v>
+      </c>
+      <c r="J76" s="3">
         <v>76331500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>77501100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>77770500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78126800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>74620200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>73028900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>72670000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71910500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>69245700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>67327900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>65506100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>60451400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>62888400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>66729900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>67336400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>70654000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>77200100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>74603800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>80850000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1324200</v>
+        <v>2127100</v>
       </c>
       <c r="E81" s="3">
+        <v>313700</v>
+      </c>
+      <c r="F81" s="3">
         <v>1821300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1534100</v>
       </c>
-      <c r="H81" s="3">
-        <v>3270700</v>
-      </c>
       <c r="I81" s="3">
+        <v>1546400</v>
+      </c>
+      <c r="J81" s="3">
         <v>1244700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>982500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1409200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2020300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1205000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1138200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1150100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>225500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>208900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>732100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>960700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>83800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>188900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-84000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-46900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>117200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>233700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>310700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>47200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>725900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>178400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>670200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,8 +7971,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7803,23 +8001,23 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
@@ -7827,8 +8025,8 @@
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7848,41 +8046,44 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>705000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>692300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>936600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>348100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>732700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>366900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>544200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>814600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,8 +8629,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8445,23 +8661,23 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
@@ -8469,8 +8685,8 @@
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -8490,41 +8706,44 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,8 +8781,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8591,32 +8811,32 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
         <v>-249000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-331000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8636,41 +8856,44 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AJ91" s="3">
         <v>-340400</v>
       </c>
       <c r="AK91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,8 +9109,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8912,23 +9141,23 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
@@ -8936,8 +9165,8 @@
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8957,41 +9186,44 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>252400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,8 +9261,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9058,8 +9291,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9125,19 +9358,22 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,8 +9699,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9486,23 +9731,23 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
@@ -9510,8 +9755,8 @@
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -9531,41 +9776,44 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>911100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,23 +9841,23 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
@@ -9617,8 +9865,8 @@
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -9638,41 +9886,44 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>875000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>430800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9700,23 +9951,23 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
@@ -9724,8 +9975,8 @@
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -9745,37 +9996,40 @@
       <c r="Z102" s="3">
         <v>0</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,247 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8705100</v>
+        <v>9293000</v>
       </c>
       <c r="E8" s="3">
+        <v>8283600</v>
+      </c>
+      <c r="F8" s="3">
         <v>7044200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7812800</v>
       </c>
-      <c r="G8" s="3">
-        <v>7622400</v>
-      </c>
       <c r="H8" s="3">
-        <v>7918900</v>
+        <v>7320300</v>
       </c>
       <c r="I8" s="3">
+        <v>7483000</v>
+      </c>
+      <c r="J8" s="3">
         <v>6822200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7288300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7651700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7941100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9102300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6928400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5707100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4801100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4626900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4467000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4179100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4479600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3846000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4143300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4898200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5964000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6438300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7751700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8073600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7778900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1005,41 +1011,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8705100</v>
+        <v>9293000</v>
       </c>
       <c r="E10" s="3">
+        <v>8283600</v>
+      </c>
+      <c r="F10" s="3">
         <v>7044200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7812800</v>
       </c>
-      <c r="G10" s="3">
-        <v>7622400</v>
-      </c>
       <c r="H10" s="3">
-        <v>7918900</v>
+        <v>7320300</v>
       </c>
       <c r="I10" s="3">
+        <v>7483000</v>
+      </c>
+      <c r="J10" s="3">
         <v>6822200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7288300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7651700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7941100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,38 +1391,41 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2220700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-75800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-49300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>696400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>146300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1485,41 +1504,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>786300</v>
+      </c>
+      <c r="E15" s="3">
         <v>426900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>408900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>338500</v>
       </c>
-      <c r="G15" s="3">
-        <v>720000</v>
-      </c>
       <c r="H15" s="3">
+        <v>569500</v>
+      </c>
+      <c r="I15" s="3">
         <v>327400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>335500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>490600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>645700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>503600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5644200</v>
+        <v>5821500</v>
       </c>
       <c r="E17" s="3">
+        <v>5645300</v>
+      </c>
+      <c r="F17" s="3">
         <v>4219900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5365800</v>
       </c>
-      <c r="G17" s="3">
-        <v>7232400</v>
-      </c>
       <c r="H17" s="3">
+        <v>7229200</v>
+      </c>
+      <c r="I17" s="3">
         <v>5721200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5353200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5465700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5971600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5928900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5351900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3346900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2292600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1996400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1733500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1605700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1446300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1589100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1539000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1706300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2354200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2969500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2912700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3733800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3942100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3931900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3061000</v>
+        <v>3471500</v>
       </c>
       <c r="E18" s="3">
+        <v>2638300</v>
+      </c>
+      <c r="F18" s="3">
         <v>2824300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2447000</v>
       </c>
-      <c r="G18" s="3">
-        <v>390000</v>
-      </c>
       <c r="H18" s="3">
-        <v>2197600</v>
+        <v>91100</v>
       </c>
       <c r="I18" s="3">
+        <v>1761800</v>
+      </c>
+      <c r="J18" s="3">
         <v>1469000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1822600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1680100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2012200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3750300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3581400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3414500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2804700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2893500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2861300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2732800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2890500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2307000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2437000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2544000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2994500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3525600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4018000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4131500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3847000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,8 +1924,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1924,119 +1957,122 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3487900</v>
+        <v>4257800</v>
       </c>
       <c r="E21" s="3">
+        <v>3065300</v>
+      </c>
+      <c r="F21" s="3">
         <v>3233300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2785500</v>
       </c>
-      <c r="G21" s="3">
-        <v>1110000</v>
-      </c>
       <c r="H21" s="3">
-        <v>2525100</v>
+        <v>660600</v>
       </c>
       <c r="I21" s="3">
+        <v>2089200</v>
+      </c>
+      <c r="J21" s="3">
         <v>1804500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2313200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2325900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2515800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2082,38 +2118,41 @@
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>326500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>822400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,8 +2183,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2222,228 +2261,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3066400</v>
+        <v>3471500</v>
       </c>
       <c r="E23" s="3">
+        <v>2643800</v>
+      </c>
+      <c r="F23" s="3">
         <v>603600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2522900</v>
       </c>
-      <c r="G23" s="3">
-        <v>439300</v>
-      </c>
       <c r="H23" s="3">
-        <v>2196600</v>
+        <v>140400</v>
       </c>
       <c r="I23" s="3">
+        <v>1760700</v>
+      </c>
+      <c r="J23" s="3">
         <v>772600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1822600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1533800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2012200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>857300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1745300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1683300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1798900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>88900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>596600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1232600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1681200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>174500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>500300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>172400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>224700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-841600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>350500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>560400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>780700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>474300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>922300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>891700</v>
+        <v>986500</v>
       </c>
       <c r="E24" s="3">
+        <v>771700</v>
+      </c>
+      <c r="F24" s="3">
         <v>254700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>665800</v>
       </c>
-      <c r="G24" s="3">
-        <v>383600</v>
-      </c>
       <c r="H24" s="3">
-        <v>631100</v>
+        <v>295700</v>
       </c>
       <c r="I24" s="3">
+        <v>506000</v>
+      </c>
+      <c r="J24" s="3">
         <v>-808000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>552500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>508700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>575800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>402000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>365600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>467600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-253700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>242300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>357600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>584000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-14000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>179600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>105800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>153800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>223000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>177600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2592800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>108900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>105300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>306800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>340400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>342600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>318600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>400600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>355700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2174700</v>
+        <v>2485000</v>
       </c>
       <c r="E26" s="3">
+        <v>1872000</v>
+      </c>
+      <c r="F26" s="3">
         <v>348900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1857000</v>
       </c>
-      <c r="G26" s="3">
-        <v>55700</v>
-      </c>
       <c r="H26" s="3">
-        <v>1565400</v>
+        <v>-155400</v>
       </c>
       <c r="I26" s="3">
+        <v>1254700</v>
+      </c>
+      <c r="J26" s="3">
         <v>1580600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1270100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1025100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1436300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2189700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1343300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1317700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1331300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>342600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>354300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>875000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1097100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>188500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>320700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>66500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>70900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>241600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>253600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>440300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>131800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>728200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>521700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>674900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2127100</v>
+        <v>1576000</v>
       </c>
       <c r="E27" s="3">
+        <v>1824500</v>
+      </c>
+      <c r="F27" s="3">
         <v>313700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1821300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-606500</v>
-      </c>
       <c r="H27" s="3">
-        <v>1534100</v>
+        <v>-818600</v>
       </c>
       <c r="I27" s="3">
+        <v>1224500</v>
+      </c>
+      <c r="J27" s="3">
         <v>1546400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1244700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>438900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1409200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2020300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1205000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1138200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1150100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>225500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>208900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>732100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>960700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>83800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>188900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-84000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-46900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>117200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>233700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>310700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>47200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>725900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>178400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>670200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2956,8 +3016,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2974,12 +3034,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2992,8 +3052,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,8 +3278,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3244,196 +3313,202 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>2893100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1836100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1731200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1005800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2804600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2264700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1500200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1209300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2132400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1936700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2371600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2769800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5035000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4859500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5244400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3496500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2127100</v>
+        <v>2431000</v>
       </c>
       <c r="E33" s="3">
+        <v>1824500</v>
+      </c>
+      <c r="F33" s="3">
         <v>313700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1821300</v>
       </c>
-      <c r="G33" s="3">
-        <v>8600</v>
-      </c>
       <c r="H33" s="3">
-        <v>1534100</v>
+        <v>-203600</v>
       </c>
       <c r="I33" s="3">
+        <v>1224500</v>
+      </c>
+      <c r="J33" s="3">
         <v>1546400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1244700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>982500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1409200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2020300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1205000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1138200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1150100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>225500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>208900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>732100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>960700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>83800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>188900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-84000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-46900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>117200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>233700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>310700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>47200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>725900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>178400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>670200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2127100</v>
+        <v>2431000</v>
       </c>
       <c r="E35" s="3">
+        <v>1824500</v>
+      </c>
+      <c r="F35" s="3">
         <v>313700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1821300</v>
       </c>
-      <c r="G35" s="3">
-        <v>8600</v>
-      </c>
       <c r="H35" s="3">
-        <v>1534100</v>
+        <v>-203600</v>
       </c>
       <c r="I35" s="3">
+        <v>1224500</v>
+      </c>
+      <c r="J35" s="3">
         <v>1546400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1244700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>982500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1409200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2020300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1205000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1138200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1150100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>225500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>208900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>732100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>960700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>83800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>188900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-84000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-46900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>117200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>233700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>310700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>47200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>725900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>178400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>670200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,261 +3932,268 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>138137400</v>
+      </c>
+      <c r="E41" s="3">
         <v>163802400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>135279000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>157295300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>144281600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>159928800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>181019100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>179591400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>163784900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>174681700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>198145200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>196741400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>192669900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>181637700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>208170000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>212033000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>209767500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>190419900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>165775900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>183905500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>181344200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>132965600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>160626300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>205606000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>189379200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>224065000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>549899000</v>
+      </c>
+      <c r="E42" s="3">
         <v>465543700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>607556700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>475900100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>448251400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>417080600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>531073300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>438541500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>436538200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>398974400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>557349900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>656241000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>579888700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>550086300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>549645200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>534165000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>514620700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>534342900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>545724400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>583172100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>643250700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>720305000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>647419900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>844378300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>764585900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>754124000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8109200</v>
+      </c>
+      <c r="E43" s="3">
         <v>9971900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45537800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10383700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1676800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10500600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46065000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8226100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1694300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8101900</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4177,8 +4269,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4209,8 +4304,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4287,40 +4382,43 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>23927900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>40413400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4397,41 +4495,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>696145600</v>
+      </c>
+      <c r="E46" s="3">
         <v>639318000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>812301500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>643579100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>594209800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>587510000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>798570800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>626368500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>602031700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>581757900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4507,338 +4608,350 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>188525000</v>
+      </c>
+      <c r="E47" s="3">
         <v>167032000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>72140000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>187103500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>156162000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>149951500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>71676800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>130016900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>134200900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>141440700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1244900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1344400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1289400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1159900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1182800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1164100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1174400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1123600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>898700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>955900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1035300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>999300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1084500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1118400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1081100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1101700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>940400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>934400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>986000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>971600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7092200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6665600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6411600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6854800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6663500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6747200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6836500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6490300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6561100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6628600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6759700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6435600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6087900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6035900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6001600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5725900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5689900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5773500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5534600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5979300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5253800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5238500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5755300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6297700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6274900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6506100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8705800</v>
+      </c>
+      <c r="E49" s="3">
         <v>8243600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8022600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8331500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8087400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8049400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8098800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7761400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7795900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7701000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7855100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7996100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7785400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7488700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7397900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7242200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7243100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7249400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6707500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7004800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7527300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7633100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8205700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9371200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9067700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10984700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,118 +5173,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>185168500</v>
+      </c>
+      <c r="E52" s="3">
         <v>187452400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31306600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>159509300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>163554100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>162672300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32293600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>151866000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>140250000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>150403100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8054500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6742500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6896400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6949400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6740900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6332200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6231600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6278200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6042200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6341600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6508400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6412400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6988100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7394000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6532500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8867400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1646056400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1531395400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1436149700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1539250500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1447986700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1435737400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1450570400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1437629100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1419533800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1419792500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,68 +5596,69 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>768781000</v>
+      </c>
+      <c r="E57" s="3">
         <v>718679200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>689782600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>724824900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>686713800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>684731900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>687559400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>647020500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>647623400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>643130200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3130100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>1761700</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>1735500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5547,71 +5677,74 @@
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>298285400</v>
+      </c>
+      <c r="E58" s="3">
         <v>252522700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>396409600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>267756000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>251066100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>241637700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>393319300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>297073500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>273882100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>257766200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5687,151 +5820,157 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56584900</v>
+      </c>
+      <c r="E59" s="3">
         <v>55089700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>114861800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56543600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57139200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52004500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>140061900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>54442200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>63190000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>66303800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>429700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>595500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>750800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>768200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>650500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>855100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>921500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>815700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>572500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>714100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>836700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>711300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>760000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>851400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2138700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1063400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>985800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1123651200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1026291600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1206347400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1049124500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>994919100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>978374200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1226229700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>998536200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>984695400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>967200100</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5907,228 +6046,237 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>261520800</v>
+      </c>
+      <c r="E61" s="3">
         <v>241588800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>122314900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>243473100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>218753900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>208782000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>113130300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>216167400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>222489100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>227269700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>206743500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>220125600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>222566500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>210513900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>220593800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>224408700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>214884000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>210056400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>196553600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>216575500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>227441600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>217812200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>220428000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>255682400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>238475100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>267994300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>165780400</v>
+      </c>
+      <c r="E62" s="3">
         <v>174706000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24640200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>160714900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>153011900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>166052400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27908700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>143983900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>132271800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>144923900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3662800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3503600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3722400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4141400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3679400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3266200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3242800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3485100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12807600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3260000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3497500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3710200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3697200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3912600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3751500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4158000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1551635900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1443233900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1353913400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1453963900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1367338500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1353861300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1367872200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1359420000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1340151700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1340068400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,8 +6991,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32301800</v>
+      </c>
+      <c r="E72" s="3">
         <v>27329200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24193000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25510800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22809400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24599200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23561400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21350600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20796900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20953900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19715300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17009100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15720900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15034800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13667200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13118800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12484400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11771300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9988000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9959700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10335300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10680000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11258500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14121700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14850900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19841400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>92709300</v>
+      </c>
+      <c r="E76" s="3">
         <v>86467800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80573600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>83553400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>78952100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>79919100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>80749400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>76331500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>77501100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>77770500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>78126800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74620200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>73028900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>72670000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71910500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>69245700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>67327900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>65506100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>60451400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>62888400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>66729900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>67336400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>70654000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>77200100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>74603800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>80850000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2127100</v>
+        <v>2431000</v>
       </c>
       <c r="E81" s="3">
+        <v>1824500</v>
+      </c>
+      <c r="F81" s="3">
         <v>313700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1821300</v>
       </c>
-      <c r="G81" s="3">
-        <v>8600</v>
-      </c>
       <c r="H81" s="3">
-        <v>1534100</v>
+        <v>-203600</v>
       </c>
       <c r="I81" s="3">
+        <v>1224500</v>
+      </c>
+      <c r="J81" s="3">
         <v>1546400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1244700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>982500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1409200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2020300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1205000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1138200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1150100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>225500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>208900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>732100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>960700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>83800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>188900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-84000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-46900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>117200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>233700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>310700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>47200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>725900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>178400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>670200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,8 +8169,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8004,23 +8202,23 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
@@ -8028,8 +8226,8 @@
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -8049,41 +8247,44 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>705000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>692300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>936600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>348100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>732700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>366900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>544200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>814600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,8 +8845,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8664,23 +8880,23 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
@@ -8688,8 +8904,8 @@
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -8709,41 +8925,44 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,8 +9001,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8814,32 +9034,32 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
         <v>-249000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-331000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-181000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8859,41 +9079,44 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AK91" s="3">
         <v>-340400</v>
       </c>
       <c r="AL91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,8 +9338,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9144,23 +9373,23 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
@@ -9168,8 +9397,8 @@
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -9189,41 +9418,44 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>252400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,8 +9494,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9294,8 +9527,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9361,19 +9594,22 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,8 +9944,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9734,23 +9979,23 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
@@ -9758,8 +10003,8 @@
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -9779,41 +10024,44 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>911100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,23 +10092,23 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
@@ -9868,8 +10116,8 @@
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -9889,41 +10137,44 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>875000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>430800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9954,23 +10205,23 @@
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
@@ -9978,8 +10229,8 @@
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -9999,37 +10250,40 @@
       <c r="AA102" s="3">
         <v>0</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7831400</v>
+      </c>
+      <c r="E8" s="3">
         <v>8947600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9121600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8283600</v>
       </c>
-      <c r="G8" s="3">
-        <v>7044200</v>
-      </c>
       <c r="H8" s="3">
+        <v>8505000</v>
+      </c>
+      <c r="I8" s="3">
         <v>7812800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8056400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7483000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6822200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7288300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7651700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7941100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9102300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6928400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5707100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4801100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4626900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4467000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4179100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4479600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3846000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4143300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4898200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5964000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6438300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7751700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8073600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7778900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1023,47 +1029,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7831400</v>
+      </c>
+      <c r="E10" s="3">
         <v>8947600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9121600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8283600</v>
       </c>
-      <c r="G10" s="3">
-        <v>7044200</v>
-      </c>
       <c r="H10" s="3">
+        <v>8505000</v>
+      </c>
+      <c r="I10" s="3">
         <v>7812800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8056400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7483000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6822200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7288300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7651700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7941100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1139,8 +1148,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,44 +1429,47 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>218400</v>
+      </c>
+      <c r="E14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-5400</v>
       </c>
-      <c r="G14" s="3">
-        <v>2220700</v>
-      </c>
       <c r="H14" s="3">
+        <v>2318000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-75800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-49300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>696400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>146300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1529,47 +1548,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>277700</v>
+      </c>
+      <c r="E15" s="3">
         <v>463500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>786300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>426900</v>
       </c>
-      <c r="G15" s="3">
-        <v>408900</v>
-      </c>
       <c r="H15" s="3">
+        <v>245900</v>
+      </c>
+      <c r="I15" s="3">
         <v>338500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>569500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>327400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>335500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>490600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>645700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>503600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1667,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6010300</v>
+      </c>
+      <c r="E17" s="3">
         <v>6076500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5818000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5645300</v>
       </c>
-      <c r="G17" s="3">
-        <v>4219900</v>
-      </c>
       <c r="H17" s="3">
+        <v>4121500</v>
+      </c>
+      <c r="I17" s="3">
         <v>5365800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7232400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5721200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5353200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5465700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5971600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5928900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5351900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3346900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2292600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1996400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1733500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1605700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1446300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1589100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1539000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1706300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2354200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2969500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2912700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3733800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3942100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3931900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1821100</v>
+      </c>
+      <c r="E18" s="3">
         <v>2871100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3303600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2638300</v>
       </c>
-      <c r="G18" s="3">
-        <v>2824300</v>
-      </c>
       <c r="H18" s="3">
+        <v>4383500</v>
+      </c>
+      <c r="I18" s="3">
         <v>2447000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>824000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1761800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1469000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1822600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1680100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2012200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3750300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3581400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3414500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2804700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2893500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2861300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2732800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2890500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2307000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2437000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2544000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2994500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3525600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4018000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4131500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3847000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,125 +2029,128 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2098700</v>
+      </c>
+      <c r="E21" s="3">
         <v>3334500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4089800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3065300</v>
       </c>
-      <c r="G21" s="3">
-        <v>3233300</v>
-      </c>
       <c r="H21" s="3">
+        <v>4629400</v>
+      </c>
+      <c r="I21" s="3">
         <v>2785500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1393400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2089200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1804500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2313200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2325900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2515800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2160,38 +2196,41 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>326500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>822400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2228,8 +2267,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2306,240 +2345,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1602700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2868700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3303600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2643800</v>
       </c>
-      <c r="G23" s="3">
-        <v>603600</v>
-      </c>
       <c r="H23" s="3">
+        <v>2065400</v>
+      </c>
+      <c r="I23" s="3">
         <v>2522900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>873200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1760700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>772600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1822600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1533800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2012200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>857300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1745300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1683300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1798900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>88900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>596600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1232600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1681200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>174500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>500300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>172400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>224700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-841600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>350500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>560400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>780700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>474300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>922300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E24" s="3">
         <v>734500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>938300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>771700</v>
       </c>
-      <c r="G24" s="3">
-        <v>254700</v>
-      </c>
       <c r="H24" s="3">
+        <v>707100</v>
+      </c>
+      <c r="I24" s="3">
         <v>665800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>507900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>506000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-808000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>552500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>508700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>575800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>402000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>365600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>467600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-253700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>242300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>357600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>584000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-14000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>179600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>105800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>153800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>223000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>177600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2592800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>108900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>105300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>306800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>340400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>342600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>318600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>400600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>355700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1466500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2134200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2365200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1872000</v>
       </c>
-      <c r="G26" s="3">
-        <v>348900</v>
-      </c>
       <c r="H26" s="3">
+        <v>1358300</v>
+      </c>
+      <c r="I26" s="3">
         <v>1857000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>365400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1254700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1580600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1270100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1025100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1436300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2189700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1343300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1317700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1331300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>342600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>354300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>875000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1097100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>188500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>320700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>66500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>70900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>241600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>253600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>440300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>131800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>728200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>521700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>674900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>488400</v>
+      </c>
+      <c r="E27" s="3">
         <v>2080300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2311200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1824500</v>
       </c>
-      <c r="G27" s="3">
-        <v>313700</v>
-      </c>
       <c r="H27" s="3">
+        <v>729900</v>
+      </c>
+      <c r="I27" s="3">
         <v>1821300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>316100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1224500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1546400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1244700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>438900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1409200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2020300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1205000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1138200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1150100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>225500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>208900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>732100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>960700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>83800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>188900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-46900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>117200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>233700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>310700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>47200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>725900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>178400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>670200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3082,8 +3142,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -3100,12 +3160,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,202 +3457,208 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>2893100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1836100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1731200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1005800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2804600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2264700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1500200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1209300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2132400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1936700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2371600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2769800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5035000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4859500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5244400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3496500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1381900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2080300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2311200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1824500</v>
       </c>
-      <c r="G33" s="3">
-        <v>313700</v>
-      </c>
       <c r="H33" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="I33" s="3">
         <v>1821300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>316100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1224500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1546400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1244700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>982500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1409200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2020300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1205000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1138200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1150100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>225500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>208900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>732100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>960700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>83800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>188900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-46900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>117200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>233700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>310700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>47200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>725900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>178400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>670200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1381900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2080300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2311200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1824500</v>
       </c>
-      <c r="G35" s="3">
-        <v>313700</v>
-      </c>
       <c r="H35" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="I35" s="3">
         <v>1821300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>316100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1224500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1546400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1244700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>982500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1409200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2020300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1205000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1138200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1150100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>225500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>208900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>732100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>960700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>83800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>188900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-46900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>117200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>233700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>310700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>47200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>725900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>178400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>670200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,279 +4104,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>162354100</v>
+      </c>
+      <c r="E41" s="3">
         <v>163843700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>144204300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>163802400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>135279000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>157295300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>144281600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>159928800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>181019100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>179591400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>163784900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>174681700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>198145200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>196741400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>192669900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>181637700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>208170000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>212033000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>209767500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>190419900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>165775900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>183905500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>181344200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>132965600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>160626300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>205606000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>189379200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>224065000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>661322100</v>
+      </c>
+      <c r="E42" s="3">
         <v>503991600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>549899000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>465543700</v>
       </c>
-      <c r="G42" s="3">
-        <v>607556700</v>
-      </c>
       <c r="H42" s="3">
+        <v>607604300</v>
+      </c>
+      <c r="I42" s="3">
         <v>475900100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>448251400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>417080600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>531073300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>438541500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>436538200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>398974400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>557349900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>656241000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>579888700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>550086300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>549645200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>534165000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>514620700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>534342900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>545724400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>583172100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>643250700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>720305000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>647419900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>844378300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>764585900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>754124000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56650200</v>
+      </c>
+      <c r="E43" s="3">
         <v>11506500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2042300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9971900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>45537800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10383700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1676800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10500600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46065000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8226100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1694300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8101900</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4367,8 +4459,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4405,8 +4500,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4483,13 +4578,16 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>74393600</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
@@ -4497,32 +4595,32 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>23927900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>40413400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -4599,47 +4697,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>954720000</v>
+      </c>
+      <c r="E46" s="3">
         <v>679341800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>696145600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>639318000</v>
       </c>
-      <c r="G46" s="3">
-        <v>812301500</v>
-      </c>
       <c r="H46" s="3">
+        <v>812349100</v>
+      </c>
+      <c r="I46" s="3">
         <v>643579100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>594209800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>587510000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>798570800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>626368500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>602031700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>581757900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,356 +4816,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>103432000</v>
+      </c>
+      <c r="E47" s="3">
         <v>180516300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>188525000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>167032000</v>
       </c>
-      <c r="G47" s="3">
-        <v>72140000</v>
-      </c>
       <c r="H47" s="3">
+        <v>66909600</v>
+      </c>
+      <c r="I47" s="3">
         <v>187103500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>156162000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>149951500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>71676800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>130016900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>134200900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>141440700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1244900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1344400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1289400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1159900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1182800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1164100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1174400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1123600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>898700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>955900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1035300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>999300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1084500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1118400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1081100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1101700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>940400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>934400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>986000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>971600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6955500</v>
+      </c>
+      <c r="E48" s="3">
         <v>7045600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7092200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6665600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6411600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6854800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6663500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6747200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6836500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6490300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6561100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6628600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6759700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6435600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6087900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6035900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6001600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5725900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5689900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5773500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5534600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5979300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5253800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5238500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5755300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6297700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6274900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6506100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8877500</v>
+      </c>
+      <c r="E49" s="3">
         <v>8800900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8705800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8243600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8022600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8331500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8087400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8049400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8098800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7761400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7795900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7701000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7855100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7996100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7785400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7488700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7397900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7242200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7243100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7249400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6707500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7004800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7527300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7633100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8205700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9371200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9067700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10984700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39216900</v>
+      </c>
+      <c r="E52" s="3">
         <v>197450400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>185168500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>187452400</v>
       </c>
-      <c r="G52" s="3">
-        <v>31306600</v>
-      </c>
       <c r="H52" s="3">
+        <v>31260000</v>
+      </c>
+      <c r="I52" s="3">
         <v>159509300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>163554100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>162672300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32293600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>151866000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>140250000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>150403100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8054500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6742500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6896400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6949400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6740900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6332200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6231600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6278200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6042200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6341600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6508400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6412400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6988100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7394000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6532500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8867400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1690587100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1632343100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1646056400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1531395400</v>
       </c>
-      <c r="G54" s="3">
-        <v>1436149700</v>
-      </c>
       <c r="H54" s="3">
+        <v>1440141800</v>
+      </c>
+      <c r="I54" s="3">
         <v>1539250500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1447986700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1435737400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1450570400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1437629100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1419533800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1419792500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,74 +5856,75 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>815521900</v>
+      </c>
+      <c r="E57" s="3">
         <v>777843500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>768781000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>718679200</v>
       </c>
-      <c r="G57" s="3">
-        <v>689782600</v>
-      </c>
       <c r="H57" s="3">
+        <v>691272400</v>
+      </c>
+      <c r="I57" s="3">
         <v>724824900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>686713800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>684731900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>687559400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>647020500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>647623400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>643130200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3130100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>1761700</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>1735500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5813,77 +5943,80 @@
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>420463800</v>
+      </c>
+      <c r="E58" s="3">
         <v>268362100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>298285400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>252522700</v>
       </c>
-      <c r="G58" s="3">
-        <v>396409600</v>
-      </c>
       <c r="H58" s="3">
+        <v>396425100</v>
+      </c>
+      <c r="I58" s="3">
         <v>267756000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>251066100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>241637700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>393319300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>297073500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>273882100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>257766200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5959,163 +6092,169 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>181929100</v>
+      </c>
+      <c r="E59" s="3">
         <v>53659500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>56584900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55089700</v>
       </c>
-      <c r="G59" s="3">
-        <v>114861800</v>
-      </c>
       <c r="H59" s="3">
+        <v>116109300</v>
+      </c>
+      <c r="I59" s="3">
         <v>56543600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>57139200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52004500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>140061900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>54442200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>63190000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66303800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>429700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>595500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>750800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>768200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>650500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>855100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>921500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>815700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>572500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>714100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>836700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>711300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>760000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>851400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2138700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1063400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>985800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1423679700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1099865100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1123651200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1026291600</v>
       </c>
-      <c r="G60" s="3">
-        <v>1206347400</v>
-      </c>
       <c r="H60" s="3">
+        <v>1209100300</v>
+      </c>
+      <c r="I60" s="3">
         <v>1049124500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>994919100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>978374200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1226229700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>998536200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>984695400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>967200100</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,240 +6330,249 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>144194000</v>
+      </c>
+      <c r="E61" s="3">
         <v>273304000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>261520800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>241588800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>122314900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>243473100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>218753900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>208782000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>113130300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>216167400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>222489100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>227269700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>206743500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>220125600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>222566500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>210513900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>220593800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>224408700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>214884000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>210056400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>196553600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>216575500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>227441600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>217812200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>220428000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>255682400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>238475100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>267994300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25403300</v>
+      </c>
+      <c r="E62" s="3">
         <v>165918100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>165780400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>174706000</v>
       </c>
-      <c r="G62" s="3">
-        <v>24640200</v>
-      </c>
       <c r="H62" s="3">
+        <v>23377200</v>
+      </c>
+      <c r="I62" s="3">
         <v>160714900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>153011900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>166052400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27908700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>143983900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>132271800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>144923900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3662800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3503600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3722400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4141400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3679400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3266200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3242800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3485100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12807600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3260000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3497500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3710200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3697200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3912600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3751500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4158000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1593974400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1539795800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1551635900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1443233900</v>
       </c>
-      <c r="G66" s="3">
-        <v>1353913400</v>
-      </c>
       <c r="H66" s="3">
+        <v>1355386700</v>
+      </c>
+      <c r="I66" s="3">
         <v>1453963900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1367338500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1353861300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1367872200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1359420000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1340151700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1340068400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>35546600</v>
+      </c>
+      <c r="E72" s="3">
         <v>31195600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>32301800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27329200</v>
       </c>
-      <c r="G72" s="3">
-        <v>24193000</v>
-      </c>
       <c r="H72" s="3">
+        <v>26785400</v>
+      </c>
+      <c r="I72" s="3">
         <v>25510800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22809400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24599200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23561400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21350600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20796900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20953900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19715300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17009100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15720900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15034800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13667200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13118800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12484400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11771300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9988000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9959700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10335300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10680000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11258500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14121700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14850900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19841400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>94778700</v>
+      </c>
+      <c r="E76" s="3">
         <v>90787300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>92709300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>86467800</v>
       </c>
-      <c r="G76" s="3">
-        <v>80573600</v>
-      </c>
       <c r="H76" s="3">
+        <v>83092500</v>
+      </c>
+      <c r="I76" s="3">
         <v>83553400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>78952100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>79919100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>80749400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>76331500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>77501100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>77770500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>78126800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>74620200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>73028900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>72670000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>71910500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>69245700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>67327900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>65506100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60451400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>62888400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>66729900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>67336400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>70654000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>77200100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>74603800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>80850000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1381900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2080300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2311200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1824500</v>
       </c>
-      <c r="G81" s="3">
-        <v>313700</v>
-      </c>
       <c r="H81" s="3">
+        <v>1324200</v>
+      </c>
+      <c r="I81" s="3">
         <v>1821300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>316100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1224500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1546400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1244700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>982500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1409200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2020300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1205000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1138200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1150100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>225500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>208900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>732100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>960700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>83800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>188900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-46900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>117200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>233700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>310700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>47200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>725900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>178400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>670200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,8 +8565,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8406,23 +8604,23 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
@@ -8430,8 +8628,8 @@
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -8451,41 +8649,44 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>705000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>692300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>936600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>348100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>732700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>366900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>544200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>814600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,8 +9277,11 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9102,23 +9318,23 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
@@ -9126,8 +9342,8 @@
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -9147,41 +9363,44 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,8 +9441,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9260,32 +9480,32 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-249000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-331000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-181000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -9305,41 +9525,44 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AL91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AM91" s="3">
         <v>-340400</v>
       </c>
       <c r="AN91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,8 +9796,11 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9608,23 +9837,23 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
@@ -9632,8 +9861,8 @@
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -9653,41 +9882,44 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>252400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,8 +9960,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9766,8 +9999,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9833,19 +10066,22 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,8 +10434,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10230,23 +10475,23 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
@@ -10254,8 +10499,8 @@
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -10275,41 +10520,44 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>911100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,23 +10594,23 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
@@ -10370,8 +10618,8 @@
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -10391,41 +10639,44 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>875000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>430800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10462,23 +10713,23 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
@@ -10486,8 +10737,8 @@
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
@@ -10507,37 +10758,40 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-18572000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,265 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9399300</v>
+      </c>
+      <c r="E8" s="3">
         <v>7831400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8947600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9121600</v>
       </c>
-      <c r="G8" s="3">
-        <v>8283600</v>
-      </c>
       <c r="H8" s="3">
+        <v>8705100</v>
+      </c>
+      <c r="I8" s="3">
         <v>8505000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7812800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8056400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7483000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6822200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7288300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7651700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7941100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9102300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6928400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5707100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4801100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4626900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4467000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4179100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4479600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3846000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4143300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4898200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5964000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6438300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7751700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8073600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7778900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1032,50 +1038,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9399300</v>
+      </c>
+      <c r="E10" s="3">
         <v>7831400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8947600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9121600</v>
       </c>
-      <c r="G10" s="3">
-        <v>8283600</v>
-      </c>
       <c r="H10" s="3">
+        <v>8705100</v>
+      </c>
+      <c r="I10" s="3">
         <v>8505000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7812800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8056400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7483000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6822200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7288300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7651700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7941100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1151,8 +1160,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,47 +1448,50 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>218400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-5400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2318000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-75800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-49300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>696400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>146300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1551,50 +1570,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>272700</v>
+      </c>
+      <c r="E15" s="3">
         <v>277700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>463500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>786300</v>
       </c>
-      <c r="G15" s="3">
-        <v>426900</v>
-      </c>
       <c r="H15" s="3">
+        <v>256700</v>
+      </c>
+      <c r="I15" s="3">
         <v>245900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>338500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>569500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>327400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>335500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>490600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>645700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>503600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1692,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5893000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6010300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6076500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5818000</v>
       </c>
-      <c r="G17" s="3">
-        <v>5645300</v>
-      </c>
       <c r="H17" s="3">
+        <v>5644200</v>
+      </c>
+      <c r="I17" s="3">
         <v>4121500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5365800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7232400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5721200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5353200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5465700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5971600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5928900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5351900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3346900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2292600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1996400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1733500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1605700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1446300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1589100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1539000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1706300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2354200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2969500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2912700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3733800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3942100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3931900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3506300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1821100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2871100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3303600</v>
       </c>
-      <c r="G18" s="3">
-        <v>2638300</v>
-      </c>
       <c r="H18" s="3">
+        <v>3061000</v>
+      </c>
+      <c r="I18" s="3">
         <v>4383500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2447000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>824000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1761800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1469000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1822600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1680100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2012200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3750300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3581400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3414500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2804700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2893500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2861300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2732800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2890500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2307000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2437000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2544000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2994500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3525600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4018000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4131500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3847000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2023,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,128 +2065,131 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3779000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2098700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3334500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4089800</v>
       </c>
-      <c r="G21" s="3">
-        <v>3065300</v>
-      </c>
       <c r="H21" s="3">
+        <v>3317700</v>
+      </c>
+      <c r="I21" s="3">
         <v>4629400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2785500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1393400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2089200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1804500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2313200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2325900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2515800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2199,38 +2235,41 @@
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>326500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>822400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2270,8 +2309,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2348,246 +2387,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3505100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1602700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2868700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3303600</v>
       </c>
-      <c r="G23" s="3">
-        <v>2643800</v>
-      </c>
       <c r="H23" s="3">
+        <v>3066400</v>
+      </c>
+      <c r="I23" s="3">
         <v>2065400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2522900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>873200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1760700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>772600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1822600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1533800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2012200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>857300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1745300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1683300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1798900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>88900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>596600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1232600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1681200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>174500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>500300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>172400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>224700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-841600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>350500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>560400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>780700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>474300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>922300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>999700</v>
+      </c>
+      <c r="E24" s="3">
         <v>136200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>734500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>938300</v>
       </c>
-      <c r="G24" s="3">
-        <v>771700</v>
-      </c>
       <c r="H24" s="3">
+        <v>891700</v>
+      </c>
+      <c r="I24" s="3">
         <v>707100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>665800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>507900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>506000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-808000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>552500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>508700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>575800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>402000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>365600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>467600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-253700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>242300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>357600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>584000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>179600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>105800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>153800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>223000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>177600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2592800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>108900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>105300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>306800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>340400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>342600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>318600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>400600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>355700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2505500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1466500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2134200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2365200</v>
       </c>
-      <c r="G26" s="3">
-        <v>1872000</v>
-      </c>
       <c r="H26" s="3">
+        <v>2174700</v>
+      </c>
+      <c r="I26" s="3">
         <v>1358300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1857000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>365400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1254700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1580600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1270100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1025100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1436300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2189700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1343300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1317700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1331300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>342600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>354300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>875000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1097100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>188500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>320700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>66500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>70900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>241600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>253600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>440300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>131800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>728200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>521700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>674900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2442100</v>
+      </c>
+      <c r="E27" s="3">
         <v>488400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2080300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2311200</v>
       </c>
-      <c r="G27" s="3">
-        <v>1824500</v>
-      </c>
       <c r="H27" s="3">
+        <v>2127100</v>
+      </c>
+      <c r="I27" s="3">
         <v>729900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1821300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>316100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1224500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1546400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1244700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>438900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1409200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2020300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1205000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1138200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1150100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>225500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>208900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>732100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>960700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>83800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>188900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-46900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>117200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>233700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>310700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>47200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>725900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>178400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>670200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3163,12 +3223,12 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3485,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,205 +3529,211 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>2893100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1836100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1731200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1005800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2804600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2264700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1500200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1209300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2132400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1936700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2371600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2769800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5035000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4859500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5244400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3496500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2442100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1381900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2080300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2311200</v>
       </c>
-      <c r="G33" s="3">
-        <v>1824500</v>
-      </c>
       <c r="H33" s="3">
+        <v>2127100</v>
+      </c>
+      <c r="I33" s="3">
         <v>1324200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1821300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>316100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1224500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1546400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1244700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>982500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1409200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2020300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1205000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1138200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1150100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>225500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>208900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>732100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>960700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>83800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>188900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-46900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>117200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>233700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>310700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>47200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>725900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>178400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>670200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2442100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1381900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2080300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2311200</v>
       </c>
-      <c r="G35" s="3">
-        <v>1824500</v>
-      </c>
       <c r="H35" s="3">
+        <v>2127100</v>
+      </c>
+      <c r="I35" s="3">
         <v>1324200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1821300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>316100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1224500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1546400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1244700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>982500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1409200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2020300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1205000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1138200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1150100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>225500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>208900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>732100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>960700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>83800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>188900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-46900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>117200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>233700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>310700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>47200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>725900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>178400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>670200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,288 +4190,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160870500</v>
+      </c>
+      <c r="E41" s="3">
         <v>162354100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>163843700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>144204300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>163802400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>135279000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>157295300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>144281600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>159928800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>181019100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>179591400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>163784900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>174681700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>198145200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>196741400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>192669900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>181637700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>208170000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>212033000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>209767500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>190419900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>165775900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>183905500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>181344200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>132965600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>160626300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>205606000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>189379200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>224065000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>557335400</v>
+      </c>
+      <c r="E42" s="3">
         <v>661322100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>503991600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>549899000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>465543700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>607604300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>475900100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>448251400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>417080600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>531073300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>438541500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>436538200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>398974400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>557349900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>656241000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>579888700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>550086300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>549645200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>534165000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>514620700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>534342900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>545724400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>583172100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>643250700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>720305000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>647419900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>844378300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>764585900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>754124000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13777200</v>
+      </c>
+      <c r="E43" s="3">
         <v>56650200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11506500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2042300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9971900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45537800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10383700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1676800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10500600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46065000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8226100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1694300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8101900</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4462,8 +4554,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4503,8 +4598,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4581,49 +4676,52 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>74393600</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>23927900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>40413400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -4700,50 +4798,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>731983200</v>
+      </c>
+      <c r="E46" s="3">
         <v>954720000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>679341800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>696145600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>639318000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>812349100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>643579100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>594209800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>587510000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>798570800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>626368500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>602031700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>581757900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4819,365 +4920,377 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>200739100</v>
+      </c>
+      <c r="E47" s="3">
         <v>103432000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>180516300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>188525000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>167032000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>66909600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>187103500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>156162000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>149951500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>71676800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>130016900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>134200900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>141440700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1244900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1344400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1289400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1159900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1182800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1164100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1174400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1123600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>898700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>955900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1035300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>999300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1084500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1118400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1081100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1101700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>940400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>934400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>986000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>971600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6841900</v>
+      </c>
+      <c r="E48" s="3">
         <v>6955500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7045600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7092200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6665600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6411600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6854800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6663500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6747200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6836500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6490300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6561100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6628600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6759700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6435600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6087900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6035900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6001600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5725900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5689900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5773500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5534600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5979300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5253800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5238500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5755300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6297700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6274900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6506100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8930000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8877500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8800900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8705800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8243600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8022600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8331500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8087400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8049400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8098800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7761400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7795900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7701000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7855100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7996100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7785400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7488700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7397900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7242200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7243100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7249400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6707500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7004800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7527300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7633100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8205700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9371200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9067700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10984700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200916600</v>
+      </c>
+      <c r="E52" s="3">
         <v>39216900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>197450400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>185168500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>187452400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31260000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>159509300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>163554100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>162672300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32293600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>151866000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>140250000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>150403100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8054500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6742500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6896400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6949400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6740900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6332200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6231600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6278200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6042200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6341600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6508400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6412400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6988100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7394000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6532500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8867400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1709935400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1690587100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1632343100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1646056400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1531395400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1440141800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1539250500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1447986700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1435737400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1450570400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1437629100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1419533800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1419792500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,77 +5986,78 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>791719100</v>
+      </c>
+      <c r="E57" s="3">
         <v>815521900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>777843500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>768781000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>718679200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>691272400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>724824900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>686713800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>684731900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>687559400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>647020500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>647623400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>643130200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3130100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>1761700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1735500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5946,80 +6076,83 @@
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>320555700</v>
+      </c>
+      <c r="E58" s="3">
         <v>420463800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>268362100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>298285400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>252522700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>396425100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>267756000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>251066100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>241637700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>393319300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>297073500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>273882100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>257766200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6095,169 +6228,175 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56113200</v>
+      </c>
+      <c r="E59" s="3">
         <v>181929100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>53659500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56584900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55089700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>116109300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>56543600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>57139200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52004500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>140061900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>54442200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>63190000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>66303800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>429700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>595500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>750800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>768200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>650500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>855100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>921500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>815700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>572500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>714100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>836700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>711300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>760000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>851400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2138700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1063400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>985800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1168388100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1423679700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1099865100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1123651200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1026291600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1209100300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1049124500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>994919100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>978374200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1226229700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>998536200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>984695400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>967200100</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6333,246 +6472,255 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>278827400</v>
+      </c>
+      <c r="E61" s="3">
         <v>144194000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>273304000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>261520800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>241588800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>122314900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>243473100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>218753900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>208782000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>113130300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>216167400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>222489100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>227269700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>206743500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>220125600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>222566500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>210513900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>220593800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>224408700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>214884000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>210056400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>196553600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>216575500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>227441600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>217812200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>220428000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>255682400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>238475100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>267994300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>170119900</v>
+      </c>
+      <c r="E62" s="3">
         <v>25403300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>165918100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>165780400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>174706000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23377200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>160714900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>153011900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>166052400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>27908700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>143983900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>132271800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>144923900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3662800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3503600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3722400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4141400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3679400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3266200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3242800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3485100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12807600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3260000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3497500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3710200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3697200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3912600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3751500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4158000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1618102200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1593974400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1539795800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1551635900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1443233900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1355386700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1453963900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1367338500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1353861300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1367872200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1359420000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1340151700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1340068400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7492,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34723900</v>
+      </c>
+      <c r="E72" s="3">
         <v>35546600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31195600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>32301800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27329200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>26785400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25510800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22809400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24599200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23561400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21350600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20796900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20953900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19715300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17009100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15720900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15034800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13667200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13118800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12484400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11771300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9988000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9959700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10335300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10680000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11258500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14121700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14850900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19841400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>89949300</v>
+      </c>
+      <c r="E76" s="3">
         <v>94778700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90787300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>92709300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>86467800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>83092500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>83553400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>78952100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>79919100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>80749400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>76331500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>77501100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77770500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>78126800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>74620200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>73028900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>72670000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>71910500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>69245700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>67327900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>65506100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60451400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>62888400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>66729900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>67336400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>70654000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>77200100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>74603800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>80850000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2442100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1381900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2080300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2311200</v>
       </c>
-      <c r="G81" s="3">
-        <v>1824500</v>
-      </c>
       <c r="H81" s="3">
+        <v>2127100</v>
+      </c>
+      <c r="I81" s="3">
         <v>1324200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1821300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>316100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1224500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1546400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1244700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>982500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1409200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2020300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1205000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1138200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1150100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>225500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>208900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>732100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>960700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>83800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>188900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-46900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>117200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>233700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>310700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>47200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>725900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>178400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>670200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,8 +8763,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8607,23 +8805,23 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
@@ -8631,8 +8829,8 @@
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -8652,41 +8850,44 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>705000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>692300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>936600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>348100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>732700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>366900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>544200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>814600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,8 +9493,11 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9321,23 +9537,23 @@
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
@@ -9345,8 +9561,8 @@
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -9366,41 +9582,44 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,8 +9661,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9483,32 +9703,32 @@
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-249000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-331000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-181000</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -9528,41 +9748,44 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AN91" s="3">
         <v>-340400</v>
       </c>
       <c r="AO91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,8 +10025,11 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9840,23 +10069,23 @@
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
@@ -9864,8 +10093,8 @@
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -9885,41 +10114,44 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>252400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,8 +10193,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10002,8 +10235,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10069,19 +10302,22 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,8 +10679,11 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10478,23 +10723,23 @@
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
@@ -10502,8 +10747,8 @@
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -10523,41 +10768,44 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>911100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,23 +10845,23 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
@@ -10621,8 +10869,8 @@
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -10642,41 +10890,44 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>875000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>430800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10716,23 +10967,23 @@
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
@@ -10740,8 +10991,8 @@
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
@@ -10761,37 +11012,40 @@
       <c r="AD102" s="3">
         <v>0</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-18572000</v>
       </c>
     </row>
